--- a/AIBQ_PBQ_Panel_2026Q2.xlsx
+++ b/AIBQ_PBQ_Panel_2026Q2.xlsx
@@ -1520,47 +1520,47 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>PBQ</t>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>AIBQ</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>FINTECH</t>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>7</v>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>4.1</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="15" t="n">
         <v>6.8</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>8.1</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M10" s="20" t="n">
-        <v>7.15</v>
+        <v>7.22</v>
       </c>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -1569,17 +1569,17 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>±3.25</t>
+          <t>±2.75</t>
         </is>
       </c>
       <c r="P10" s="18" t="inlineStr">
         <is>
-          <t>$44.03B post</t>
+          <t>$965B post</t>
         </is>
       </c>
       <c r="Q10" s="18" t="inlineStr">
         <is>
-          <t>$1.0B (FY2025)  [Net]</t>
+          <t>$47B gross run-rate (May 2026)  [GROSS]</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
@@ -1607,20 +1607,20 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n">
-        <v>7.5</v>
+      <c r="F11" s="15" t="n">
+        <v>7.2</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0.25</v>
       </c>
       <c r="M11" s="20" t="n">
-        <v>6.98</v>
+        <v>7.15</v>
       </c>
       <c r="N11" s="21" t="inlineStr">
         <is>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="P11" s="18" t="inlineStr">
         <is>
-          <t>$17.3B</t>
+          <t>$44.03B post</t>
         </is>
       </c>
       <c r="Q11" s="18" t="inlineStr">
         <is>
-          <t>$1.3B (TTM 4Q2025)  [Mixed]</t>
+          <t>$1.0B (FY2025)  [Net]</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>DEFENSE</t>
+          <t>FINTECH</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -1676,20 +1676,20 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="F12" s="15" t="n">
-        <v>6.2</v>
+      <c r="F12" s="13" t="n">
+        <v>7.5</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>4.5</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>0.25</v>
       </c>
       <c r="M12" s="20" t="n">
-        <v>6.94</v>
+        <v>6.98</v>
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>±3.0</t>
+          <t>±3.25</t>
         </is>
       </c>
       <c r="P12" s="18" t="inlineStr">
         <is>
-          <t>$61B post</t>
+          <t>$17.3B</t>
         </is>
       </c>
       <c r="Q12" s="18" t="inlineStr">
         <is>
-          <t>$2.15B (FY2025)  [Gross]</t>
+          <t>$1.3B (TTM 4Q2025)  [Mixed]</t>
         </is>
       </c>
     </row>
@@ -1727,17 +1727,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>AIBQ</t>
+          <t>Anduril Industries</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>PBQ</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>AI-AUTO</t>
+          <t>DEFENSE</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -1745,17 +1745,17 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>7.8</v>
+      <c r="F13" s="15" t="n">
+        <v>6.2</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>6.7</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>7.3</v>
@@ -1767,7 +1767,7 @@
         <v>0.25</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>±3.25</t>
+          <t>±3.0</t>
         </is>
       </c>
       <c r="P13" s="18" t="inlineStr">
         <is>
-          <t>$15B</t>
+          <t>$61B post</t>
         </is>
       </c>
       <c r="Q13" s="18" t="inlineStr">
         <is>
-          <t>$800M (TTM 4Q2025)  [Net]</t>
+          <t>$2.15B (FY2025)  [Gross]</t>
         </is>
       </c>
     </row>
@@ -1796,47 +1796,47 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Epic Games</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>PBQ</t>
+          <t>Applied Intuition</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>AIBQ</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H14" s="15" t="n">
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G14" s="15" t="n">
         <v>7.2</v>
       </c>
-      <c r="I14" s="14" t="n">
-        <v>5.8</v>
+      <c r="H14" s="22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>6.5</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M14" s="20" t="n">
-        <v>6.89</v>
+        <v>6.91</v>
       </c>
       <c r="N14" s="21" t="inlineStr">
         <is>
@@ -1845,17 +1845,17 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>±3.75</t>
+          <t>±3.25</t>
         </is>
       </c>
       <c r="P14" s="18" t="inlineStr">
         <is>
-          <t>$22.5B (2024; stale)</t>
+          <t>$15B</t>
         </is>
       </c>
       <c r="Q14" s="18" t="inlineStr">
         <is>
-          <t>$6.21B (TTM 4Q2025)  [Gross bookings-derived]</t>
+          <t>$800M (TTM 4Q2025)  [Net]</t>
         </is>
       </c>
     </row>
@@ -1865,17 +1865,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>AIBQ</t>
+          <t>Epic Games</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>PBQ</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>AI-INFRA</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1883,20 +1883,20 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>8.1</v>
+      <c r="F15" s="15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>7.2</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0.5</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>6.82</v>
+        <v>6.89</v>
       </c>
       <c r="N15" s="21" t="inlineStr">
         <is>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>±2.75</t>
+          <t>±3.75</t>
         </is>
       </c>
       <c r="P15" s="18" t="inlineStr">
         <is>
-          <t>$965B post</t>
+          <t>$22.5B (2024; stale)</t>
         </is>
       </c>
       <c r="Q15" s="18" t="inlineStr">
         <is>
-          <t>$47B gross run-rate (May 2026)  [GROSS]</t>
+          <t>$6.21B (TTM 4Q2025)  [Gross bookings-derived]</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -2082,37 +2082,37 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>AI-APP</t>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>7.1</v>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>4.9</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>7.9</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M18" s="23" t="n">
-        <v>6.05</v>
+        <v>6.3</v>
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
@@ -2121,17 +2121,17 @@
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>±3.25</t>
+          <t>±2.75</t>
         </is>
       </c>
       <c r="P18" s="18" t="inlineStr">
         <is>
-          <t>$60B (SpaceX all-stock acquisition, pending)</t>
+          <t>$852B</t>
         </is>
       </c>
       <c r="Q18" s="18" t="inlineStr">
         <is>
-          <t>~$4B ARR (run-rate, Jun 2026)  [Gross]</t>
+          <t>~$25B net run-rate (Mar 2026)  [NET]</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -2151,37 +2151,37 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>AI-INFRA</t>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>3.3</v>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>7.1</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>6.3</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M19" s="23" t="n">
-        <v>5.96</v>
+        <v>6.05</v>
       </c>
       <c r="N19" s="24" t="inlineStr">
         <is>
@@ -2190,17 +2190,17 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>±2.75</t>
+          <t>±3.25</t>
         </is>
       </c>
       <c r="P19" s="18" t="inlineStr">
         <is>
-          <t>$852B</t>
+          <t>$60B (SpaceX all-stock acquisition, pending)</t>
         </is>
       </c>
       <c r="Q19" s="18" t="inlineStr">
         <is>
-          <t>~$25B net run-rate (Mar 2026)  [NET]</t>
+          <t>~$4B ARR (run-rate, Jun 2026)  [Gross]</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
     <row r="190">
       <c r="A190" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B190" s="29" t="inlineStr">
@@ -9369,24 +9369,24 @@
       <c r="D190" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E190" s="42" t="n">
-        <v>7</v>
+      <c r="E190" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F190" s="33" t="inlineStr">
         <is>
-          <t>S4 Bessemer: rapid net-new ARR on modest burn; still investing but efficient for scale</t>
+          <t>S5 EI gate fails -&gt; fix#2 Bessemer fallback: net-new ARR ~$23-38B vs ~$25B net burn ~=0.9-1.0x = growth-EFFICIENT; absolute-loss sits in CE-2/CE-4 not double-counted</t>
         </is>
       </c>
       <c r="G190" s="31" t="inlineStr">
         <is>
-          <t>Est/PB(T4)</t>
+          <t>Web/Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B191" s="29" t="inlineStr">
@@ -9402,24 +9402,24 @@
       <c r="D191" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E191" s="36" t="n">
-        <v>7.5</v>
+      <c r="E191" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F191" s="33" t="inlineStr">
         <is>
-          <t>Software+interchange GM est ~65-72%; FINTECH no sector bonus</t>
+          <t>GM ~40% (below AI-INFRA &gt;50% bonus threshold); improving to 63%E</t>
         </is>
       </c>
       <c r="G191" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B192" s="29" t="inlineStr">
@@ -9436,23 +9436,23 @@
         <v>0.2</v>
       </c>
       <c r="E192" s="42" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F192" s="33" t="inlineStr">
         <is>
-          <t>Burn improving as revenue scales 33%+/yr</t>
+          <t>Burn trajectory improving; Q2 first operating profit</t>
         </is>
       </c>
       <c r="G192" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B193" s="29" t="inlineStr">
@@ -9468,17 +9468,17 @@
       <c r="D193" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E193" s="36" t="n">
-        <v>7.5</v>
+      <c r="E193" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F193" s="33" t="inlineStr">
         <is>
-          <t>$3.6B raised, up-round access, low debt reliance</t>
+          <t>$124.3B equity + $37B debt; heavy dilution/leverage</t>
         </is>
       </c>
       <c r="G193" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
       <c r="C194" s="37" t="n"/>
       <c r="D194" s="37" t="n"/>
       <c r="E194" s="39" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="F194" s="37" t="n"/>
       <c r="G194" s="37" t="n"/>
@@ -9500,7 +9500,7 @@
     <row r="195">
       <c r="A195" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B195" s="29" t="inlineStr">
@@ -9517,23 +9517,23 @@
         <v>0.3</v>
       </c>
       <c r="E195" s="36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F195" s="33" t="inlineStr">
         <is>
-          <t>High NRR ~120-130% (spend grows with customer)</t>
+          <t>NRR 140%+</t>
         </is>
       </c>
       <c r="G195" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B196" s="29" t="inlineStr">
@@ -9549,24 +9549,24 @@
       <c r="D196" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E196" s="36" t="n">
-        <v>8</v>
+      <c r="E196" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="F196" s="33" t="inlineStr">
         <is>
-          <t>Broad SMB/mid-market base; low single-customer concentration</t>
+          <t>Cloud-partner reseller concentration; Amazon/Google both investors+partners (-1.0 modifier applies)</t>
         </is>
       </c>
       <c r="G196" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B197" s="29" t="inlineStr">
@@ -9582,24 +9582,24 @@
       <c r="D197" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E197" s="42" t="n">
-        <v>7</v>
+      <c r="E197" s="36" t="n">
+        <v>9</v>
       </c>
       <c r="F197" s="33" t="inlineStr">
         <is>
-          <t>Moving upmarket; growing enterprise/$100K ACV cohort</t>
+          <t>~80% enterprise; 1,000+ at $1M+ ACV; deep F500</t>
         </is>
       </c>
       <c r="G197" s="31" t="inlineStr">
         <is>
-          <t>Web/PB(T3)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -9615,12 +9615,12 @@
       <c r="D198" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E198" s="42" t="n">
-        <v>6.5</v>
+      <c r="E198" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F198" s="33" t="inlineStr">
         <is>
-          <t>Card spend largely on-demand; committed share moderate</t>
+          <t>Growing committed enterprise contracts</t>
         </is>
       </c>
       <c r="G198" s="31" t="inlineStr">
@@ -9632,7 +9632,7 @@
     <row r="199">
       <c r="A199" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B199" s="29" t="inlineStr">
@@ -9648,17 +9648,17 @@
       <c r="D199" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E199" s="42" t="n">
-        <v>7</v>
+      <c r="E199" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F199" s="33" t="inlineStr">
         <is>
-          <t>Pricing power via savings-share model; low churn</t>
+          <t>Maintained per-token value; Opus pricing power</t>
         </is>
       </c>
       <c r="G199" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       <c r="C200" s="37" t="n"/>
       <c r="D200" s="37" t="n"/>
       <c r="E200" s="39" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="F200" s="37" t="n"/>
       <c r="G200" s="37" t="n"/>
@@ -9680,165 +9680,165 @@
     <row r="201">
       <c r="A201" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B201" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C201" s="31" t="inlineStr">
         <is>
-          <t>SV-1</t>
+          <t>CI-1</t>
         </is>
       </c>
       <c r="D201" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E201" s="36" t="n">
-        <v>8.5</v>
+      <c r="E201" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="F201" s="33" t="inlineStr">
         <is>
-          <t>Very high release cadence; expanded bill-pay/procurement/treasury/travel</t>
+          <t>Genuine multi-provider/multi-arch (AWS Trainium + Google TPU + SpaceX Colossus GPU), no single &gt;~50%; but rents all training compute</t>
         </is>
       </c>
       <c r="G201" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B202" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C202" s="31" t="inlineStr">
         <is>
-          <t>SV-2</t>
+          <t>CI-2</t>
         </is>
       </c>
       <c r="D202" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E202" s="40" t="n">
-        <v>4.5</v>
+        <v>0.25</v>
+      </c>
+      <c r="E202" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="F202" s="33" t="inlineStr">
         <is>
-          <t>Primarily US; limited international entities</t>
+          <t>No owned DC/fab; buys Alphabet-designed chips (debt-financed)</t>
         </is>
       </c>
       <c r="G202" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B203" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C203" s="31" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>CI-3</t>
         </is>
       </c>
       <c r="D203" s="31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E203" s="36" t="n">
-        <v>7.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="E203" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="F203" s="33" t="inlineStr">
         <is>
-          <t>Deep accounting/ERP integrations; developer API</t>
+          <t>No owned power/PPA</t>
         </is>
       </c>
       <c r="G203" s="31" t="inlineStr">
         <is>
-          <t>Web/PB(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B204" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C204" s="31" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>CI-4</t>
         </is>
       </c>
       <c r="D204" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E204" s="42" t="n">
-        <v>6.5</v>
+      <c r="E204" s="40" t="n">
+        <v>4.5</v>
       </c>
       <c r="F204" s="33" t="inlineStr">
         <is>
-          <t>Tuck-in M&amp;A (Cohere.io, Venue, Billhop)</t>
+          <t>Diversifies silicon (Trainium/TPU/GPU) — less TSMC-single-point</t>
         </is>
       </c>
       <c r="G204" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B205" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C205" s="31" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>CI-5</t>
         </is>
       </c>
       <c r="D205" s="31" t="n">
         <v>0.1</v>
       </c>
       <c r="E205" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F205" s="33" t="inlineStr">
         <is>
-          <t>Ships ahead of Brex/Navan on several features</t>
+          <t>Colossus 90-day termination, retains all IP</t>
         </is>
       </c>
       <c r="G205" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>SEC(T1)</t>
         </is>
       </c>
     </row>
@@ -9846,13 +9846,13 @@
       <c r="A206" s="37" t="n"/>
       <c r="B206" s="38" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)  →  Dimension score</t>
+          <t>Compute Independence (15%)  →  Dimension score</t>
         </is>
       </c>
       <c r="C206" s="37" t="n"/>
       <c r="D206" s="37" t="n"/>
       <c r="E206" s="39" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="F206" s="37" t="n"/>
       <c r="G206" s="37" t="n"/>
@@ -9860,7 +9860,7 @@
     <row r="207">
       <c r="A207" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B207" s="29" t="inlineStr">
@@ -9876,12 +9876,12 @@
       <c r="D207" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E207" s="40" t="n">
-        <v>5.5</v>
+      <c r="E207" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F207" s="33" t="inlineStr">
         <is>
-          <t>Founder-led board; some institutional independents, no public-co slate yet</t>
+          <t>LTBT + independent directors; S-1 governance maturing</t>
         </is>
       </c>
       <c r="G207" s="31" t="inlineStr">
@@ -9893,7 +9893,7 @@
     <row r="208">
       <c r="A208" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B208" s="29" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="F208" s="33" t="inlineStr">
         <is>
-          <t>Clean pref stack, weighted-avg anti-dilution, non-participating (per Series F terms)</t>
+          <t>PBC + Long-Term Benefit Trust; complex but disclosed</t>
         </is>
       </c>
       <c r="G208" s="31" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="209">
       <c r="A209" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B209" s="29" t="inlineStr">
@@ -9942,24 +9942,24 @@
       <c r="D209" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E209" s="40" t="n">
-        <v>5.5</v>
+      <c r="E209" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F209" s="33" t="inlineStr">
         <is>
-          <t>No banker mandate/S-1 yet; strong cap markets investors</t>
+          <t>Confidential S-1 filed; bankers engaged; audit-grade</t>
         </is>
       </c>
       <c r="G209" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B210" s="29" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F210" s="33" t="inlineStr">
         <is>
-          <t>No material litigation/investigations known</t>
+          <t>Copyright suits (industry-wide) but manageable; strong safety posture</t>
         </is>
       </c>
       <c r="G210" s="31" t="inlineStr">
@@ -9992,7 +9992,7 @@
     <row r="211">
       <c r="A211" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B211" s="29" t="inlineStr">
@@ -10008,12 +10008,12 @@
       <c r="D211" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E211" s="42" t="n">
-        <v>6.5</v>
+      <c r="E211" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F211" s="33" t="inlineStr">
         <is>
-          <t>Stable co-CEO founders (Glyman/Kirkpatrick); deep bench</t>
+          <t>Stable founder team (Amodei); deep research bench</t>
         </is>
       </c>
       <c r="G211" s="31" t="inlineStr">
@@ -10032,7 +10032,7 @@
       <c r="C212" s="37" t="n"/>
       <c r="D212" s="37" t="n"/>
       <c r="E212" s="39" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="F212" s="37" t="n"/>
       <c r="G212" s="37" t="n"/>
@@ -10040,7 +10040,7 @@
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B213" s="29" t="inlineStr">
@@ -10056,24 +10056,24 @@
       <c r="D213" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E213" s="42" t="n">
-        <v>6</v>
+      <c r="E213" s="36" t="n">
+        <v>8.5</v>
       </c>
       <c r="F213" s="33" t="inlineStr">
         <is>
-          <t>No proprietary frontier model; edge is workflow breadth (cap self-benchmark)</t>
+          <t>Frontier benchmark leadership (Opus 4.8 agentic lead) — but many self-published (cap direction-high/magnitude-low)</t>
         </is>
       </c>
       <c r="G213" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -10089,12 +10089,12 @@
       <c r="D214" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E214" s="42" t="n">
-        <v>7</v>
+      <c r="E214" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F214" s="33" t="inlineStr">
         <is>
-          <t>Spend data gravity + ERP embedding raises switching cost</t>
+          <t>Enterprise/API + Claude Code embedding; some switching cost</t>
         </is>
       </c>
       <c r="G214" s="31" t="inlineStr">
@@ -10106,7 +10106,7 @@
     <row r="215">
       <c r="A215" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B215" s="29" t="inlineStr">
@@ -10122,24 +10122,24 @@
       <c r="D215" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E215" s="42" t="n">
-        <v>7</v>
+      <c r="E215" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F215" s="33" t="inlineStr">
         <is>
-          <t>Strong talent retention; hires from fintech incumbents</t>
+          <t>Elite research talent; net hires from rivals</t>
         </is>
       </c>
       <c r="G215" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B216" s="29" t="inlineStr">
@@ -10156,11 +10156,11 @@
         <v>0.15</v>
       </c>
       <c r="E216" s="36" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F216" s="33" t="inlineStr">
         <is>
-          <t>Proprietary spend dataset feeds savings/AI features</t>
+          <t>Proprietary RLHF/safety data + Claude Code usage flywheel</t>
         </is>
       </c>
       <c r="G216" s="31" t="inlineStr">
@@ -10172,7 +10172,7 @@
     <row r="217">
       <c r="A217" s="28" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B217" s="29" t="inlineStr">
@@ -10188,17 +10188,17 @@
       <c r="D217" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E217" s="42" t="n">
-        <v>7</v>
+      <c r="E217" s="36" t="n">
+        <v>8.5</v>
       </c>
       <c r="F217" s="33" t="inlineStr">
         <is>
-          <t>Top-3 brand in modern spend management</t>
+          <t>Top-tier brand; ~54% coding share</t>
         </is>
       </c>
       <c r="G217" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       <c r="C218" s="37" t="n"/>
       <c r="D218" s="37" t="n"/>
       <c r="E218" s="39" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="F218" s="37" t="n"/>
       <c r="G218" s="37" t="n"/>
@@ -10221,17 +10221,17 @@
       <c r="A219" s="37" t="n"/>
       <c r="B219" s="44" t="inlineStr">
         <is>
-          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.25)</t>
+          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.5)</t>
         </is>
       </c>
       <c r="C219" s="37" t="n"/>
       <c r="D219" s="37" t="n"/>
       <c r="E219" s="47" t="n">
-        <v>7.15</v>
+        <v>7.22</v>
       </c>
       <c r="F219" s="46" t="inlineStr">
         <is>
-          <t>Tier: Strong   ·   Confidence ±3.25   ·   CRA weak-dims=0</t>
+          <t>Tier: Strong   ·   Confidence ±2.75   ·   CRA weak-dims=0</t>
         </is>
       </c>
       <c r="G219" s="37" t="n"/>
@@ -10239,7 +10239,7 @@
     <row r="221">
       <c r="A221" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B221" s="29" t="inlineStr">
@@ -10255,24 +10255,24 @@
       <c r="D221" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E221" s="36" t="n">
-        <v>8</v>
+      <c r="E221" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F221" s="33" t="inlineStr">
         <is>
-          <t>S4: profitable, positive net-new ARR vs low burn -&gt; strong Bessemer</t>
+          <t>S4 Bessemer: rapid net-new ARR on modest burn; still investing but efficient for scale</t>
         </is>
       </c>
       <c r="G221" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Est/PB(T4)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B222" s="29" t="inlineStr">
@@ -10288,12 +10288,12 @@
       <c r="D222" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E222" s="42" t="n">
-        <v>6.5</v>
+      <c r="E222" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F222" s="33" t="inlineStr">
         <is>
-          <t>Blended GM solid on software; EOR flows dilute headline; FINTECH no bonus</t>
+          <t>Software+interchange GM est ~65-72%; FINTECH no sector bonus</t>
         </is>
       </c>
       <c r="G222" s="31" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <row r="223">
       <c r="A223" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B223" s="29" t="inlineStr">
@@ -10321,24 +10321,24 @@
       <c r="D223" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E223" s="36" t="n">
-        <v>7.5</v>
+      <c r="E223" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F223" s="33" t="inlineStr">
         <is>
-          <t>Reached profitability -&gt; burn trend strongly positive</t>
+          <t>Burn improving as revenue scales 33%+/yr</t>
         </is>
       </c>
       <c r="G223" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B224" s="29" t="inlineStr">
@@ -10355,11 +10355,11 @@
         <v>0.15</v>
       </c>
       <c r="E224" s="36" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F224" s="33" t="inlineStr">
         <is>
-          <t>Only ~$983M raised for $17B co = highly capital-efficient</t>
+          <t>$3.6B raised, up-round access, low debt reliance</t>
         </is>
       </c>
       <c r="G224" s="31" t="inlineStr">
@@ -10378,7 +10378,7 @@
       <c r="C225" s="37" t="n"/>
       <c r="D225" s="37" t="n"/>
       <c r="E225" s="39" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="F225" s="37" t="n"/>
       <c r="G225" s="37" t="n"/>
@@ -10386,7 +10386,7 @@
     <row r="226">
       <c r="A226" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B226" s="29" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="F226" s="33" t="inlineStr">
         <is>
-          <t>Land-and-expand across payroll modules; NRR ~120%</t>
+          <t>High NRR ~120-130% (spend grows with customer)</t>
         </is>
       </c>
       <c r="G226" s="31" t="inlineStr">
@@ -10419,7 +10419,7 @@
     <row r="227">
       <c r="A227" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B227" s="29" t="inlineStr">
@@ -10436,11 +10436,11 @@
         <v>0.2</v>
       </c>
       <c r="E227" s="36" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F227" s="33" t="inlineStr">
         <is>
-          <t>Diversified SMB-&gt;enterprise base; low concentration</t>
+          <t>Broad SMB/mid-market base; low single-customer concentration</t>
         </is>
       </c>
       <c r="G227" s="31" t="inlineStr">
@@ -10452,7 +10452,7 @@
     <row r="228">
       <c r="A228" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B228" s="29" t="inlineStr">
@@ -10473,19 +10473,19 @@
       </c>
       <c r="F228" s="33" t="inlineStr">
         <is>
-          <t>Growing enterprise/multinational logos</t>
+          <t>Moving upmarket; growing enterprise/$100K ACV cohort</t>
         </is>
       </c>
       <c r="G228" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web/PB(T3)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B229" s="29" t="inlineStr">
@@ -10502,11 +10502,11 @@
         <v>0.15</v>
       </c>
       <c r="E229" s="42" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F229" s="33" t="inlineStr">
         <is>
-          <t>Payroll contracts sticky/recurring</t>
+          <t>Card spend largely on-demand; committed share moderate</t>
         </is>
       </c>
       <c r="G229" s="31" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="230">
       <c r="A230" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -10535,11 +10535,11 @@
         <v>0.15</v>
       </c>
       <c r="E230" s="42" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F230" s="33" t="inlineStr">
         <is>
-          <t>Pricing power via compliance breadth</t>
+          <t>Pricing power via savings-share model; low churn</t>
         </is>
       </c>
       <c r="G230" s="31" t="inlineStr">
@@ -10558,7 +10558,7 @@
       <c r="C231" s="37" t="n"/>
       <c r="D231" s="37" t="n"/>
       <c r="E231" s="39" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F231" s="37" t="n"/>
       <c r="G231" s="37" t="n"/>
@@ -10566,7 +10566,7 @@
     <row r="232">
       <c r="A232" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B232" s="29" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="F232" s="33" t="inlineStr">
         <is>
-          <t>Very rapid module expansion (EOR, payroll, PEO, IT, immigration)</t>
+          <t>Very high release cadence; expanded bill-pay/procurement/treasury/travel</t>
         </is>
       </c>
       <c r="G232" s="31" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="233">
       <c r="A233" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B233" s="29" t="inlineStr">
@@ -10615,24 +10615,24 @@
       <c r="D233" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E233" s="36" t="n">
-        <v>9</v>
+      <c r="E233" s="40" t="n">
+        <v>4.5</v>
       </c>
       <c r="F233" s="33" t="inlineStr">
         <is>
-          <t>150+ countries with payroll/compliance entities (best-in-panel geographies)</t>
+          <t>Primarily US; limited international entities</t>
         </is>
       </c>
       <c r="G233" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B234" s="29" t="inlineStr">
@@ -10653,19 +10653,19 @@
       </c>
       <c r="F234" s="33" t="inlineStr">
         <is>
-          <t>Broad HRIS/accounting integrations + API</t>
+          <t>Deep accounting/ERP integrations; developer API</t>
         </is>
       </c>
       <c r="G234" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Web/PB(T3)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B235" s="29" t="inlineStr">
@@ -10681,24 +10681,24 @@
       <c r="D235" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E235" s="36" t="n">
-        <v>7.5</v>
+      <c r="E235" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F235" s="33" t="inlineStr">
         <is>
-          <t>Serial acquirer (Capbase, Assemble, PaySpace, Zavvy)</t>
+          <t>Tuck-in M&amp;A (Cohere.io, Venue, Billhop)</t>
         </is>
       </c>
       <c r="G235" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B236" s="29" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="F236" s="33" t="inlineStr">
         <is>
-          <t>Ships fast vs Rippling/Remote</t>
+          <t>Ships ahead of Brex/Navan on several features</t>
         </is>
       </c>
       <c r="G236" s="31" t="inlineStr">
@@ -10738,7 +10738,7 @@
       <c r="C237" s="37" t="n"/>
       <c r="D237" s="37" t="n"/>
       <c r="E237" s="39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F237" s="37" t="n"/>
       <c r="G237" s="37" t="n"/>
@@ -10746,7 +10746,7 @@
     <row r="238">
       <c r="A238" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B238" s="29" t="inlineStr">
@@ -10763,23 +10763,23 @@
         <v>0.25</v>
       </c>
       <c r="E238" s="40" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F238" s="33" t="inlineStr">
         <is>
-          <t>Founder-controlled; espionage scandal raises governance concern</t>
+          <t>Founder-led board; some institutional independents, no public-co slate yet</t>
         </is>
       </c>
       <c r="G238" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B239" s="29" t="inlineStr">
@@ -10795,24 +10795,24 @@
       <c r="D239" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E239" s="40" t="n">
-        <v>5.5</v>
+      <c r="E239" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F239" s="33" t="inlineStr">
         <is>
-          <t>Standard late-stage terms; founder influence</t>
+          <t>Clean pref stack, weighted-avg anti-dilution, non-participating (per Series F terms)</t>
         </is>
       </c>
       <c r="G239" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B240" s="29" t="inlineStr">
@@ -10829,11 +10829,11 @@
         <v>0.2</v>
       </c>
       <c r="E240" s="40" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F240" s="33" t="inlineStr">
         <is>
-          <t>Profitable but no S-1; audit maturity unclear</t>
+          <t>No banker mandate/S-1 yet; strong cap markets investors</t>
         </is>
       </c>
       <c r="G240" s="31" t="inlineStr">
@@ -10845,7 +10845,7 @@
     <row r="241">
       <c r="A241" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B241" s="29" t="inlineStr">
@@ -10861,24 +10861,24 @@
       <c r="D241" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E241" s="41" t="n">
-        <v>2.5</v>
+      <c r="E241" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F241" s="33" t="inlineStr">
         <is>
-          <t>Active DOJ investigation + RICO/trade-secret defendant in Rippling suit -&gt; major overhang</t>
+          <t>No material litigation/investigations known</t>
         </is>
       </c>
       <c r="G241" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B242" s="29" t="inlineStr">
@@ -10894,17 +10894,17 @@
       <c r="D242" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E242" s="40" t="n">
-        <v>5.5</v>
+      <c r="E242" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F242" s="33" t="inlineStr">
         <is>
-          <t>Founder team intact; reputational risk from scandal</t>
+          <t>Stable co-CEO founders (Glyman/Kirkpatrick); deep bench</t>
         </is>
       </c>
       <c r="G242" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       <c r="C243" s="37" t="n"/>
       <c r="D243" s="37" t="n"/>
       <c r="E243" s="39" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F243" s="37" t="n"/>
       <c r="G243" s="37" t="n"/>
@@ -10926,7 +10926,7 @@
     <row r="244">
       <c r="A244" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B244" s="29" t="inlineStr">
@@ -10942,12 +10942,12 @@
       <c r="D244" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E244" s="40" t="n">
-        <v>5</v>
+      <c r="E244" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F244" s="33" t="inlineStr">
         <is>
-          <t>No proprietary model moat; compliance breadth is the edge (cap self-claims)</t>
+          <t>No proprietary frontier model; edge is workflow breadth (cap self-benchmark)</t>
         </is>
       </c>
       <c r="G244" s="31" t="inlineStr">
@@ -10959,7 +10959,7 @@
     <row r="245">
       <c r="A245" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B245" s="29" t="inlineStr">
@@ -10975,12 +10975,12 @@
       <c r="D245" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E245" s="36" t="n">
-        <v>7.5</v>
+      <c r="E245" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F245" s="33" t="inlineStr">
         <is>
-          <t>Payroll/compliance embedding = high switching cost</t>
+          <t>Spend data gravity + ERP embedding raises switching cost</t>
         </is>
       </c>
       <c r="G245" s="31" t="inlineStr">
@@ -10992,7 +10992,7 @@
     <row r="246">
       <c r="A246" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -11009,11 +11009,11 @@
         <v>0.2</v>
       </c>
       <c r="E246" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F246" s="33" t="inlineStr">
         <is>
-          <t>Talent retention pressured by litigation publicity</t>
+          <t>Strong talent retention; hires from fintech incumbents</t>
         </is>
       </c>
       <c r="G246" s="31" t="inlineStr">
@@ -11025,7 +11025,7 @@
     <row r="247">
       <c r="A247" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B247" s="29" t="inlineStr">
@@ -11041,12 +11041,12 @@
       <c r="D247" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E247" s="42" t="n">
-        <v>7</v>
+      <c r="E247" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F247" s="33" t="inlineStr">
         <is>
-          <t>Proprietary global compliance/localization dataset</t>
+          <t>Proprietary spend dataset feeds savings/AI features</t>
         </is>
       </c>
       <c r="G247" s="31" t="inlineStr">
@@ -11058,7 +11058,7 @@
     <row r="248">
       <c r="A248" s="28" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="B248" s="29" t="inlineStr">
@@ -11074,12 +11074,12 @@
       <c r="D248" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E248" s="36" t="n">
-        <v>7.5</v>
+      <c r="E248" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F248" s="33" t="inlineStr">
         <is>
-          <t>Leading brand in global payroll/EOR</t>
+          <t>Top-3 brand in modern spend management</t>
         </is>
       </c>
       <c r="G248" s="31" t="inlineStr">
@@ -11098,7 +11098,7 @@
       <c r="C249" s="37" t="n"/>
       <c r="D249" s="37" t="n"/>
       <c r="E249" s="39" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="F249" s="37" t="n"/>
       <c r="G249" s="37" t="n"/>
@@ -11113,7 +11113,7 @@
       <c r="C250" s="37" t="n"/>
       <c r="D250" s="37" t="n"/>
       <c r="E250" s="47" t="n">
-        <v>6.98</v>
+        <v>7.15</v>
       </c>
       <c r="F250" s="46" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
     <row r="252">
       <c r="A252" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B252" s="29" t="inlineStr">
@@ -11141,24 +11141,24 @@
       <c r="D252" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E252" s="42" t="n">
-        <v>7</v>
+      <c r="E252" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F252" s="33" t="inlineStr">
         <is>
-          <t>S4 Bessemer: strong net-new revenue vs heavy capex (Arsenal-1); scaling efficiently</t>
+          <t>S4: profitable, positive net-new ARR vs low burn -&gt; strong Bessemer</t>
         </is>
       </c>
       <c r="G252" s="31" t="inlineStr">
         <is>
-          <t>Web/Est(T3)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B253" s="29" t="inlineStr">
@@ -11174,12 +11174,12 @@
       <c r="D253" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E253" s="40" t="n">
-        <v>4.5</v>
+      <c r="E253" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F253" s="33" t="inlineStr">
         <is>
-          <t>Hardware GM ~30-40%; DEFENSE gets no CE-2 sector bonus</t>
+          <t>Blended GM solid on software; EOR flows dilute headline; FINTECH no bonus</t>
         </is>
       </c>
       <c r="G253" s="31" t="inlineStr">
@@ -11191,7 +11191,7 @@
     <row r="254">
       <c r="A254" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B254" s="29" t="inlineStr">
@@ -11207,24 +11207,24 @@
       <c r="D254" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E254" s="42" t="n">
-        <v>6</v>
+      <c r="E254" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F254" s="33" t="inlineStr">
         <is>
-          <t>Burn/capex high but funded; improving unit economics</t>
+          <t>Reached profitability -&gt; burn trend strongly positive</t>
         </is>
       </c>
       <c r="G254" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B255" s="29" t="inlineStr">
@@ -11240,12 +11240,12 @@
       <c r="D255" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E255" s="42" t="n">
-        <v>7</v>
+      <c r="E255" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F255" s="33" t="inlineStr">
         <is>
-          <t>$11.9B raised, $61B mark, minimal debt</t>
+          <t>Only ~$983M raised for $17B co = highly capital-efficient</t>
         </is>
       </c>
       <c r="G255" s="31" t="inlineStr">
@@ -11264,7 +11264,7 @@
       <c r="C256" s="37" t="n"/>
       <c r="D256" s="37" t="n"/>
       <c r="E256" s="39" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="F256" s="37" t="n"/>
       <c r="G256" s="37" t="n"/>
@@ -11272,7 +11272,7 @@
     <row r="257">
       <c r="A257" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B257" s="29" t="inlineStr">
@@ -11288,12 +11288,12 @@
       <c r="D257" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E257" s="42" t="n">
-        <v>7</v>
+      <c r="E257" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F257" s="33" t="inlineStr">
         <is>
-          <t>Program-based; expanding wallet with DoD (proxy NRR high)</t>
+          <t>Land-and-expand across payroll modules; NRR ~120%</t>
         </is>
       </c>
       <c r="G257" s="31" t="inlineStr">
@@ -11305,7 +11305,7 @@
     <row r="258">
       <c r="A258" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B258" s="29" t="inlineStr">
@@ -11321,12 +11321,12 @@
       <c r="D258" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E258" s="40" t="n">
-        <v>5.5</v>
+      <c r="E258" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F258" s="33" t="inlineStr">
         <is>
-          <t>Concentrated in US DoD/allied govts (single buyer-class risk)</t>
+          <t>Diversified SMB-&gt;enterprise base; low concentration</t>
         </is>
       </c>
       <c r="G258" s="31" t="inlineStr">
@@ -11338,7 +11338,7 @@
     <row r="259">
       <c r="A259" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B259" s="29" t="inlineStr">
@@ -11354,24 +11354,24 @@
       <c r="D259" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E259" s="36" t="n">
-        <v>8</v>
+      <c r="E259" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F259" s="33" t="inlineStr">
         <is>
-          <t>Almost entirely large govt/enterprise contracts; multiple &gt;$1B programs</t>
+          <t>Growing enterprise/multinational logos</t>
         </is>
       </c>
       <c r="G259" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B260" s="29" t="inlineStr">
@@ -11387,24 +11387,24 @@
       <c r="D260" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E260" s="36" t="n">
-        <v>8</v>
+      <c r="E260" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F260" s="33" t="inlineStr">
         <is>
-          <t>Multi-year IDIQs ($20B/$1B ceilings) = high committed backlog</t>
+          <t>Payroll contracts sticky/recurring</t>
         </is>
       </c>
       <c r="G260" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B261" s="29" t="inlineStr">
@@ -11421,11 +11421,11 @@
         <v>0.15</v>
       </c>
       <c r="E261" s="42" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="F261" s="33" t="inlineStr">
         <is>
-          <t>Pricing disciplined vs primes; competitive bids</t>
+          <t>Pricing power via compliance breadth</t>
         </is>
       </c>
       <c r="G261" s="31" t="inlineStr">
@@ -11444,7 +11444,7 @@
       <c r="C262" s="37" t="n"/>
       <c r="D262" s="37" t="n"/>
       <c r="E262" s="39" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="F262" s="37" t="n"/>
       <c r="G262" s="37" t="n"/>
@@ -11452,7 +11452,7 @@
     <row r="263">
       <c r="A263" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B263" s="29" t="inlineStr">
@@ -11468,12 +11468,12 @@
       <c r="D263" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E263" s="42" t="n">
-        <v>7</v>
+      <c r="E263" s="36" t="n">
+        <v>8.5</v>
       </c>
       <c r="F263" s="33" t="inlineStr">
         <is>
-          <t>Broad product family (Ghost, Roadrunner, Fury, Lattice, Barracuda)</t>
+          <t>Very rapid module expansion (EOR, payroll, PEO, IT, immigration)</t>
         </is>
       </c>
       <c r="G263" s="31" t="inlineStr">
@@ -11485,7 +11485,7 @@
     <row r="264">
       <c r="A264" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B264" s="29" t="inlineStr">
@@ -11501,12 +11501,12 @@
       <c r="D264" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E264" s="42" t="n">
-        <v>6</v>
+      <c r="E264" s="36" t="n">
+        <v>9</v>
       </c>
       <c r="F264" s="33" t="inlineStr">
         <is>
-          <t>US + allied nations (UK, AUS, others)</t>
+          <t>150+ countries with payroll/compliance entities (best-in-panel geographies)</t>
         </is>
       </c>
       <c r="G264" s="31" t="inlineStr">
@@ -11518,7 +11518,7 @@
     <row r="265">
       <c r="A265" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B265" s="29" t="inlineStr">
@@ -11534,12 +11534,12 @@
       <c r="D265" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E265" s="42" t="n">
-        <v>6.5</v>
+      <c r="E265" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F265" s="33" t="inlineStr">
         <is>
-          <t>Lattice as integration platform/SDK across systems</t>
+          <t>Broad HRIS/accounting integrations + API</t>
         </is>
       </c>
       <c r="G265" s="31" t="inlineStr">
@@ -11551,7 +11551,7 @@
     <row r="266">
       <c r="A266" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B266" s="29" t="inlineStr">
@@ -11567,24 +11567,24 @@
       <c r="D266" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E266" s="42" t="n">
-        <v>7</v>
+      <c r="E266" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F266" s="33" t="inlineStr">
         <is>
-          <t>Active acquirer (Dive, Blue Force, ExoAnalytic)</t>
+          <t>Serial acquirer (Capbase, Assemble, PaySpace, Zavvy)</t>
         </is>
       </c>
       <c r="G266" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B267" s="29" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="F267" s="33" t="inlineStr">
         <is>
-          <t>Rapid fielding vs traditional primes</t>
+          <t>Ships fast vs Rippling/Remote</t>
         </is>
       </c>
       <c r="G267" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       <c r="C268" s="37" t="n"/>
       <c r="D268" s="37" t="n"/>
       <c r="E268" s="39" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="F268" s="37" t="n"/>
       <c r="G268" s="37" t="n"/>
@@ -11632,7 +11632,7 @@
     <row r="269">
       <c r="A269" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B269" s="29" t="inlineStr">
@@ -11648,24 +11648,24 @@
       <c r="D269" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E269" s="42" t="n">
-        <v>6</v>
+      <c r="E269" s="40" t="n">
+        <v>4.5</v>
       </c>
       <c r="F269" s="33" t="inlineStr">
         <is>
-          <t>Institutional board; not yet public-co independent majority</t>
+          <t>Founder-controlled; espionage scandal raises governance concern</t>
         </is>
       </c>
       <c r="G269" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B270" s="29" t="inlineStr">
@@ -11681,12 +11681,12 @@
       <c r="D270" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E270" s="42" t="n">
-        <v>6</v>
+      <c r="E270" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F270" s="33" t="inlineStr">
         <is>
-          <t>Clean later-stage structure; founder influence</t>
+          <t>Standard late-stage terms; founder influence</t>
         </is>
       </c>
       <c r="G270" s="31" t="inlineStr">
@@ -11698,7 +11698,7 @@
     <row r="271">
       <c r="A271" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B271" s="29" t="inlineStr">
@@ -11715,11 +11715,11 @@
         <v>0.2</v>
       </c>
       <c r="E271" s="40" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F271" s="33" t="inlineStr">
         <is>
-          <t>IPO-track profile; no S-1 filed yet</t>
+          <t>Profitable but no S-1; audit maturity unclear</t>
         </is>
       </c>
       <c r="G271" s="31" t="inlineStr">
@@ -11731,7 +11731,7 @@
     <row r="272">
       <c r="A272" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B272" s="29" t="inlineStr">
@@ -11747,12 +11747,12 @@
       <c r="D272" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E272" s="42" t="n">
-        <v>7.3</v>
+      <c r="E272" s="41" t="n">
+        <v>2.5</v>
       </c>
       <c r="F272" s="33" t="inlineStr">
         <is>
-          <t>Deep govt contracts + security clearances (+0.3 defense accreditation); no material litigation</t>
+          <t>Active DOJ investigation + RICO/trade-secret defendant in Rippling suit -&gt; major overhang</t>
         </is>
       </c>
       <c r="G272" s="31" t="inlineStr">
@@ -11764,7 +11764,7 @@
     <row r="273">
       <c r="A273" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B273" s="29" t="inlineStr">
@@ -11780,17 +11780,17 @@
       <c r="D273" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E273" s="42" t="n">
-        <v>7</v>
+      <c r="E273" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F273" s="33" t="inlineStr">
         <is>
-          <t>Stable founder/exec team (Luckey/Schimpf/Brose)</t>
+          <t>Founder team intact; reputational risk from scandal</t>
         </is>
       </c>
       <c r="G273" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       <c r="C274" s="37" t="n"/>
       <c r="D274" s="37" t="n"/>
       <c r="E274" s="39" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="F274" s="37" t="n"/>
       <c r="G274" s="37" t="n"/>
@@ -11812,7 +11812,7 @@
     <row r="275">
       <c r="A275" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B275" s="29" t="inlineStr">
@@ -11828,24 +11828,24 @@
       <c r="D275" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E275" s="42" t="n">
-        <v>7</v>
+      <c r="E275" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="F275" s="33" t="inlineStr">
         <is>
-          <t>Lattice autonomy + hardware IP; hard-to-replicate systems integration</t>
+          <t>No proprietary model moat; compliance breadth is the edge (cap self-claims)</t>
         </is>
       </c>
       <c r="G275" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B276" s="29" t="inlineStr">
@@ -11862,11 +11862,11 @@
         <v>0.25</v>
       </c>
       <c r="E276" s="36" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F276" s="33" t="inlineStr">
         <is>
-          <t>Program lock-in + certification/recert = very high switching cost</t>
+          <t>Payroll/compliance embedding = high switching cost</t>
         </is>
       </c>
       <c r="G276" s="31" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="277">
       <c r="A277" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -11895,11 +11895,11 @@
         <v>0.2</v>
       </c>
       <c r="E277" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F277" s="33" t="inlineStr">
         <is>
-          <t>Attracts elite defense-tech talent; strong retention</t>
+          <t>Talent retention pressured by litigation publicity</t>
         </is>
       </c>
       <c r="G277" s="31" t="inlineStr">
@@ -11911,7 +11911,7 @@
     <row r="278">
       <c r="A278" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -11928,11 +11928,11 @@
         <v>0.15</v>
       </c>
       <c r="E278" s="42" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F278" s="33" t="inlineStr">
         <is>
-          <t>Proprietary sensor/mission data; growing</t>
+          <t>Proprietary global compliance/localization dataset</t>
         </is>
       </c>
       <c r="G278" s="31" t="inlineStr">
@@ -11944,7 +11944,7 @@
     <row r="279">
       <c r="A279" s="28" t="inlineStr">
         <is>
-          <t>Anduril Industries</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="B279" s="29" t="inlineStr">
@@ -11961,11 +11961,11 @@
         <v>0.15</v>
       </c>
       <c r="E279" s="36" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F279" s="33" t="inlineStr">
         <is>
-          <t>Category-defining brand in defense tech</t>
+          <t>Leading brand in global payroll/EOR</t>
         </is>
       </c>
       <c r="G279" s="31" t="inlineStr">
@@ -11984,7 +11984,7 @@
       <c r="C280" s="37" t="n"/>
       <c r="D280" s="37" t="n"/>
       <c r="E280" s="39" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="F280" s="37" t="n"/>
       <c r="G280" s="37" t="n"/>
@@ -11999,11 +11999,11 @@
       <c r="C281" s="37" t="n"/>
       <c r="D281" s="37" t="n"/>
       <c r="E281" s="47" t="n">
-        <v>6.94</v>
+        <v>6.98</v>
       </c>
       <c r="F281" s="46" t="inlineStr">
         <is>
-          <t>Tier: Strong   ·   Confidence ±3.0   ·   CRA weak-dims=0</t>
+          <t>Tier: Strong   ·   Confidence ±3.25   ·   CRA weak-dims=0</t>
         </is>
       </c>
       <c r="G281" s="37" t="n"/>
@@ -12011,7 +12011,7 @@
     <row r="283">
       <c r="A283" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B283" s="29" t="inlineStr">
@@ -12027,24 +12027,24 @@
       <c r="D283" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E283" s="36" t="n">
-        <v>8</v>
+      <c r="E283" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F283" s="33" t="inlineStr">
         <is>
-          <t>S4 Bessemer: profitable, strong net-new on modest burn</t>
+          <t>S4 Bessemer: strong net-new revenue vs heavy capex (Arsenal-1); scaling efficiently</t>
         </is>
       </c>
       <c r="G283" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Web/Est(T3)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B284" s="29" t="inlineStr">
@@ -12060,12 +12060,12 @@
       <c r="D284" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E284" s="36" t="n">
-        <v>7.5</v>
+      <c r="E284" s="40" t="n">
+        <v>4.5</v>
       </c>
       <c r="F284" s="33" t="inlineStr">
         <is>
-          <t>~70%+ software GM; AI-AUTO no infra bonus</t>
+          <t>Hardware GM ~30-40%; DEFENSE gets no CE-2 sector bonus</t>
         </is>
       </c>
       <c r="G284" s="31" t="inlineStr">
@@ -12077,7 +12077,7 @@
     <row r="285">
       <c r="A285" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B285" s="29" t="inlineStr">
@@ -12093,24 +12093,24 @@
       <c r="D285" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E285" s="36" t="n">
-        <v>7.5</v>
+      <c r="E285" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F285" s="33" t="inlineStr">
         <is>
-          <t>Profitable -&gt; favorable burn trajectory</t>
+          <t>Burn/capex high but funded; improving unit economics</t>
         </is>
       </c>
       <c r="G285" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B286" s="29" t="inlineStr">
@@ -12126,12 +12126,12 @@
       <c r="D286" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E286" s="36" t="n">
-        <v>8</v>
+      <c r="E286" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F286" s="33" t="inlineStr">
         <is>
-          <t>Only $1.2B raised for $15B co = very capital-efficient</t>
+          <t>$11.9B raised, $61B mark, minimal debt</t>
         </is>
       </c>
       <c r="G286" s="31" t="inlineStr">
@@ -12150,7 +12150,7 @@
       <c r="C287" s="37" t="n"/>
       <c r="D287" s="37" t="n"/>
       <c r="E287" s="39" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="F287" s="37" t="n"/>
       <c r="G287" s="37" t="n"/>
@@ -12158,7 +12158,7 @@
     <row r="288">
       <c r="A288" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B288" s="29" t="inlineStr">
@@ -12174,12 +12174,12 @@
       <c r="D288" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E288" s="36" t="n">
-        <v>7.5</v>
+      <c r="E288" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F288" s="33" t="inlineStr">
         <is>
-          <t>Expanding within OEM/defense accounts</t>
+          <t>Program-based; expanding wallet with DoD (proxy NRR high)</t>
         </is>
       </c>
       <c r="G288" s="31" t="inlineStr">
@@ -12191,7 +12191,7 @@
     <row r="289">
       <c r="A289" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B289" s="29" t="inlineStr">
@@ -12207,12 +12207,12 @@
       <c r="D289" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E289" s="42" t="n">
-        <v>6</v>
+      <c r="E289" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F289" s="33" t="inlineStr">
         <is>
-          <t>Concentrated in a handful of large OEM/defense programs</t>
+          <t>Concentrated in US DoD/allied govts (single buyer-class risk)</t>
         </is>
       </c>
       <c r="G289" s="31" t="inlineStr">
@@ -12224,7 +12224,7 @@
     <row r="290">
       <c r="A290" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B290" s="29" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F290" s="33" t="inlineStr">
         <is>
-          <t>Nearly all enterprise/govt; large contracts</t>
+          <t>Almost entirely large govt/enterprise contracts; multiple &gt;$1B programs</t>
         </is>
       </c>
       <c r="G290" s="31" t="inlineStr">
@@ -12257,7 +12257,7 @@
     <row r="291">
       <c r="A291" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B291" s="29" t="inlineStr">
@@ -12274,23 +12274,23 @@
         <v>0.15</v>
       </c>
       <c r="E291" s="36" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F291" s="33" t="inlineStr">
         <is>
-          <t>Multi-year program commitments</t>
+          <t>Multi-year IDIQs ($20B/$1B ceilings) = high committed backlog</t>
         </is>
       </c>
       <c r="G291" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B292" s="29" t="inlineStr">
@@ -12307,11 +12307,11 @@
         <v>0.15</v>
       </c>
       <c r="E292" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F292" s="33" t="inlineStr">
         <is>
-          <t>Strong pricing in specialized niche</t>
+          <t>Pricing disciplined vs primes; competitive bids</t>
         </is>
       </c>
       <c r="G292" s="31" t="inlineStr">
@@ -12330,7 +12330,7 @@
       <c r="C293" s="37" t="n"/>
       <c r="D293" s="37" t="n"/>
       <c r="E293" s="39" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="F293" s="37" t="n"/>
       <c r="G293" s="37" t="n"/>
@@ -12338,165 +12338,165 @@
     <row r="294">
       <c r="A294" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C294" s="31" t="inlineStr">
         <is>
-          <t>CI-1</t>
+          <t>SV-1</t>
         </is>
       </c>
       <c r="D294" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E294" s="40" t="n">
-        <v>4</v>
+      <c r="E294" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F294" s="33" t="inlineStr">
         <is>
-          <t>Runs on cloud + customer compute; simulation is compute-heavy but not own</t>
+          <t>Broad product family (Ghost, Roadrunner, Fury, Lattice, Barracuda)</t>
         </is>
       </c>
       <c r="G294" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B295" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C295" s="31" t="inlineStr">
         <is>
-          <t>CI-2</t>
+          <t>SV-2</t>
         </is>
       </c>
       <c r="D295" s="31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E295" s="41" t="n">
-        <v>3</v>
+        <v>0.2</v>
+      </c>
+      <c r="E295" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F295" s="33" t="inlineStr">
         <is>
-          <t>No owned DC/silicon</t>
+          <t>US + allied nations (UK, AUS, others)</t>
         </is>
       </c>
       <c r="G295" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B296" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C296" s="31" t="inlineStr">
         <is>
-          <t>CI-3</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="D296" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E296" s="41" t="n">
-        <v>3</v>
+        <v>0.25</v>
+      </c>
+      <c r="E296" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F296" s="33" t="inlineStr">
         <is>
-          <t>No owned power</t>
+          <t>Lattice as integration platform/SDK across systems</t>
         </is>
       </c>
       <c r="G296" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B297" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C297" s="31" t="inlineStr">
         <is>
-          <t>CI-4</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="D297" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E297" s="40" t="n">
-        <v>4</v>
+      <c r="E297" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F297" s="33" t="inlineStr">
         <is>
-          <t>Indirect GPU dependence</t>
+          <t>Active acquirer (Dive, Blue Force, ExoAnalytic)</t>
         </is>
       </c>
       <c r="G297" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B298" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C298" s="31" t="inlineStr">
         <is>
-          <t>CI-5</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="D298" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="E298" s="40" t="n">
-        <v>5</v>
+      <c r="E298" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F298" s="33" t="inlineStr">
         <is>
-          <t>Flexible compute contracts</t>
+          <t>Rapid fielding vs traditional primes</t>
         </is>
       </c>
       <c r="G298" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
@@ -12504,13 +12504,13 @@
       <c r="A299" s="37" t="n"/>
       <c r="B299" s="38" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)  →  Dimension score</t>
+          <t>Strategic Velocity (15%)  →  Dimension score</t>
         </is>
       </c>
       <c r="C299" s="37" t="n"/>
       <c r="D299" s="37" t="n"/>
       <c r="E299" s="39" t="n">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="F299" s="37" t="n"/>
       <c r="G299" s="37" t="n"/>
@@ -12518,7 +12518,7 @@
     <row r="300">
       <c r="A300" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B300" s="29" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="F300" s="33" t="inlineStr">
         <is>
-          <t>Institutional board; not public-co yet</t>
+          <t>Institutional board; not yet public-co independent majority</t>
         </is>
       </c>
       <c r="G300" s="31" t="inlineStr">
@@ -12551,7 +12551,7 @@
     <row r="301">
       <c r="A301" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B301" s="29" t="inlineStr">
@@ -12568,11 +12568,11 @@
         <v>0.2</v>
       </c>
       <c r="E301" s="42" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F301" s="33" t="inlineStr">
         <is>
-          <t>Clean structure; founder-led</t>
+          <t>Clean later-stage structure; founder influence</t>
         </is>
       </c>
       <c r="G301" s="31" t="inlineStr">
@@ -12584,7 +12584,7 @@
     <row r="302">
       <c r="A302" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B302" s="29" t="inlineStr">
@@ -12600,12 +12600,12 @@
       <c r="D302" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E302" s="42" t="n">
-        <v>6</v>
+      <c r="E302" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F302" s="33" t="inlineStr">
         <is>
-          <t>Profitable; audit-capable; no S-1</t>
+          <t>IPO-track profile; no S-1 filed yet</t>
         </is>
       </c>
       <c r="G302" s="31" t="inlineStr">
@@ -12617,7 +12617,7 @@
     <row r="303">
       <c r="A303" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B303" s="29" t="inlineStr">
@@ -12633,24 +12633,24 @@
       <c r="D303" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E303" s="36" t="n">
-        <v>7.5</v>
+      <c r="E303" s="42" t="n">
+        <v>7.3</v>
       </c>
       <c r="F303" s="33" t="inlineStr">
         <is>
-          <t>Defense/ITAR posture; no material litigation</t>
+          <t>Deep govt contracts + security clearances (+0.3 defense accreditation); no material litigation</t>
         </is>
       </c>
       <c r="G303" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B304" s="29" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="F304" s="33" t="inlineStr">
         <is>
-          <t>Stable founders (Younis/Chen ex-Google)</t>
+          <t>Stable founder/exec team (Luckey/Schimpf/Brose)</t>
         </is>
       </c>
       <c r="G304" s="31" t="inlineStr">
@@ -12690,7 +12690,7 @@
       <c r="C305" s="37" t="n"/>
       <c r="D305" s="37" t="n"/>
       <c r="E305" s="39" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="F305" s="37" t="n"/>
       <c r="G305" s="37" t="n"/>
@@ -12698,7 +12698,7 @@
     <row r="306">
       <c r="A306" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B306" s="29" t="inlineStr">
@@ -12719,19 +12719,19 @@
       </c>
       <c r="F306" s="33" t="inlineStr">
         <is>
-          <t>Specialized autonomy/sim IP; strong but self-measured (cap)</t>
+          <t>Lattice autonomy + hardware IP; hard-to-replicate systems integration</t>
         </is>
       </c>
       <c r="G306" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B307" s="29" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F307" s="33" t="inlineStr">
         <is>
-          <t>Deep OEM toolchain integration = high switching cost</t>
+          <t>Program lock-in + certification/recert = very high switching cost</t>
         </is>
       </c>
       <c r="G307" s="31" t="inlineStr">
@@ -12764,7 +12764,7 @@
     <row r="308">
       <c r="A308" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B308" s="29" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="F308" s="33" t="inlineStr">
         <is>
-          <t>Elite autonomy/robotics talent</t>
+          <t>Attracts elite defense-tech talent; strong retention</t>
         </is>
       </c>
       <c r="G308" s="31" t="inlineStr">
@@ -12797,7 +12797,7 @@
     <row r="309">
       <c r="A309" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B309" s="29" t="inlineStr">
@@ -12814,11 +12814,11 @@
         <v>0.15</v>
       </c>
       <c r="E309" s="42" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F309" s="33" t="inlineStr">
         <is>
-          <t>Proprietary driving-scenario datasets</t>
+          <t>Proprietary sensor/mission data; growing</t>
         </is>
       </c>
       <c r="G309" s="31" t="inlineStr">
@@ -12830,7 +12830,7 @@
     <row r="310">
       <c r="A310" s="28" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">
@@ -12847,11 +12847,11 @@
         <v>0.15</v>
       </c>
       <c r="E310" s="36" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F310" s="33" t="inlineStr">
         <is>
-          <t>Leading AV-simulation brand</t>
+          <t>Category-defining brand in defense tech</t>
         </is>
       </c>
       <c r="G310" s="31" t="inlineStr">
@@ -12885,11 +12885,11 @@
       <c r="C312" s="37" t="n"/>
       <c r="D312" s="37" t="n"/>
       <c r="E312" s="47" t="n">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
       <c r="F312" s="46" t="inlineStr">
         <is>
-          <t>Tier: Strong   ·   Confidence ±3.25   ·   CRA weak-dims=0</t>
+          <t>Tier: Strong   ·   Confidence ±3.0   ·   CRA weak-dims=0</t>
         </is>
       </c>
       <c r="G312" s="37" t="n"/>
@@ -12897,7 +12897,7 @@
     <row r="314">
       <c r="A314" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B314" s="29" t="inlineStr">
@@ -12913,24 +12913,24 @@
       <c r="D314" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E314" s="42" t="n">
-        <v>6.5</v>
+      <c r="E314" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F314" s="33" t="inlineStr">
         <is>
-          <t>S5: profitable at times but Fortnite-cyclical; treat as mid Bessemer/EI</t>
+          <t>S4 Bessemer: profitable, strong net-new on modest burn</t>
         </is>
       </c>
       <c r="G314" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B315" s="29" t="inlineStr">
@@ -12946,12 +12946,12 @@
       <c r="D315" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E315" s="42" t="n">
-        <v>6</v>
+      <c r="E315" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F315" s="33" t="inlineStr">
         <is>
-          <t>Blended GM pressured by store rev-share payouts</t>
+          <t>~70%+ software GM; AI-AUTO no infra bonus</t>
         </is>
       </c>
       <c r="G315" s="31" t="inlineStr">
@@ -12963,7 +12963,7 @@
     <row r="316">
       <c r="A316" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B316" s="29" t="inlineStr">
@@ -12979,24 +12979,24 @@
       <c r="D316" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E316" s="42" t="n">
-        <v>6</v>
+      <c r="E316" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F316" s="33" t="inlineStr">
         <is>
-          <t>Post-2023 layoffs improved burn; stabilized</t>
+          <t>Profitable -&gt; favorable burn trajectory</t>
         </is>
       </c>
       <c r="G316" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B317" s="29" t="inlineStr">
@@ -13012,12 +13012,12 @@
       <c r="D317" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E317" s="42" t="n">
-        <v>6.5</v>
+      <c r="E317" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F317" s="33" t="inlineStr">
         <is>
-          <t>Disney capital; modest dilution; strong cash gen</t>
+          <t>Only $1.2B raised for $15B co = very capital-efficient</t>
         </is>
       </c>
       <c r="G317" s="31" t="inlineStr">
@@ -13036,7 +13036,7 @@
       <c r="C318" s="37" t="n"/>
       <c r="D318" s="37" t="n"/>
       <c r="E318" s="39" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="F318" s="37" t="n"/>
       <c r="G318" s="37" t="n"/>
@@ -13044,7 +13044,7 @@
     <row r="319">
       <c r="A319" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B319" s="29" t="inlineStr">
@@ -13060,12 +13060,12 @@
       <c r="D319" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E319" s="40" t="n">
-        <v>5.5</v>
+      <c r="E319" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F319" s="33" t="inlineStr">
         <is>
-          <t>Consumer bookings volatile with Fortnite seasonality (no classic NRR)</t>
+          <t>Expanding within OEM/defense accounts</t>
         </is>
       </c>
       <c r="G319" s="31" t="inlineStr">
@@ -13077,7 +13077,7 @@
     <row r="320">
       <c r="A320" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B320" s="29" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="F320" s="33" t="inlineStr">
         <is>
-          <t>Fortnite is a large share of bookings -&gt; title concentration</t>
+          <t>Concentrated in a handful of large OEM/defense programs</t>
         </is>
       </c>
       <c r="G320" s="31" t="inlineStr">
@@ -13110,7 +13110,7 @@
     <row r="321">
       <c r="A321" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B321" s="29" t="inlineStr">
@@ -13126,24 +13126,24 @@
       <c r="D321" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E321" s="42" t="n">
-        <v>6</v>
+      <c r="E321" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F321" s="33" t="inlineStr">
         <is>
-          <t>Unreal Engine enterprise licensing broadens base</t>
+          <t>Nearly all enterprise/govt; large contracts</t>
         </is>
       </c>
       <c r="G321" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B322" s="29" t="inlineStr">
@@ -13159,12 +13159,12 @@
       <c r="D322" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E322" s="40" t="n">
-        <v>5.5</v>
+      <c r="E322" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F322" s="33" t="inlineStr">
         <is>
-          <t>Limited committed/recurring; transactional</t>
+          <t>Multi-year program commitments</t>
         </is>
       </c>
       <c r="G322" s="31" t="inlineStr">
@@ -13176,7 +13176,7 @@
     <row r="323">
       <c r="A323" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B323" s="29" t="inlineStr">
@@ -13193,11 +13193,11 @@
         <v>0.15</v>
       </c>
       <c r="E323" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F323" s="33" t="inlineStr">
         <is>
-          <t>Pricing power in Unreal; store 12% take undercuts rivals</t>
+          <t>Strong pricing in specialized niche</t>
         </is>
       </c>
       <c r="G323" s="31" t="inlineStr">
@@ -13216,7 +13216,7 @@
       <c r="C324" s="37" t="n"/>
       <c r="D324" s="37" t="n"/>
       <c r="E324" s="39" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="F324" s="37" t="n"/>
       <c r="G324" s="37" t="n"/>
@@ -13224,28 +13224,28 @@
     <row r="325">
       <c r="A325" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B325" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C325" s="31" t="inlineStr">
         <is>
-          <t>SV-1</t>
+          <t>CI-1</t>
         </is>
       </c>
       <c r="D325" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E325" s="42" t="n">
-        <v>7</v>
+      <c r="E325" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F325" s="33" t="inlineStr">
         <is>
-          <t>Steady Unreal/Fortnite/UEFN releases</t>
+          <t>Runs on cloud + customer compute; simulation is compute-heavy but not own</t>
         </is>
       </c>
       <c r="G325" s="31" t="inlineStr">
@@ -13257,28 +13257,28 @@
     <row r="326">
       <c r="A326" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B326" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C326" s="31" t="inlineStr">
         <is>
-          <t>SV-2</t>
+          <t>CI-2</t>
         </is>
       </c>
       <c r="D326" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E326" s="36" t="n">
-        <v>8</v>
+        <v>0.25</v>
+      </c>
+      <c r="E326" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="F326" s="33" t="inlineStr">
         <is>
-          <t>Global consumer footprint</t>
+          <t>No owned DC/silicon</t>
         </is>
       </c>
       <c r="G326" s="31" t="inlineStr">
@@ -13290,28 +13290,28 @@
     <row r="327">
       <c r="A327" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B327" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C327" s="31" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>CI-3</t>
         </is>
       </c>
       <c r="D327" s="31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E327" s="36" t="n">
-        <v>7.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="E327" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="F327" s="33" t="inlineStr">
         <is>
-          <t>Unreal ecosystem, marketplace, huge dev integrations</t>
+          <t>No owned power</t>
         </is>
       </c>
       <c r="G327" s="31" t="inlineStr">
@@ -13323,61 +13323,61 @@
     <row r="328">
       <c r="A328" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B328" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C328" s="31" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>CI-4</t>
         </is>
       </c>
       <c r="D328" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E328" s="42" t="n">
-        <v>6.5</v>
+      <c r="E328" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F328" s="33" t="inlineStr">
         <is>
-          <t>Acquisitive (Bandcamp hist., Fab, Loci, Meshcapade)</t>
+          <t>Indirect GPU dependence</t>
         </is>
       </c>
       <c r="G328" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B329" s="29" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)</t>
+          <t>Compute Independence (15%)</t>
         </is>
       </c>
       <c r="C329" s="31" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>CI-5</t>
         </is>
       </c>
       <c r="D329" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="E329" s="42" t="n">
-        <v>7</v>
+      <c r="E329" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="F329" s="33" t="inlineStr">
         <is>
-          <t>Engine tech leadership</t>
+          <t>Flexible compute contracts</t>
         </is>
       </c>
       <c r="G329" s="31" t="inlineStr">
@@ -13390,13 +13390,13 @@
       <c r="A330" s="37" t="n"/>
       <c r="B330" s="38" t="inlineStr">
         <is>
-          <t>Strategic Velocity (15%)  →  Dimension score</t>
+          <t>Compute Independence (15%)  →  Dimension score</t>
         </is>
       </c>
       <c r="C330" s="37" t="n"/>
       <c r="D330" s="37" t="n"/>
       <c r="E330" s="39" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="F330" s="37" t="n"/>
       <c r="G330" s="37" t="n"/>
@@ -13404,7 +13404,7 @@
     <row r="331">
       <c r="A331" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B331" s="29" t="inlineStr">
@@ -13420,24 +13420,24 @@
       <c r="D331" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E331" s="40" t="n">
-        <v>5.5</v>
+      <c r="E331" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F331" s="33" t="inlineStr">
         <is>
-          <t>Tencent ~40% + founder control; limited independence</t>
+          <t>Institutional board; not public-co yet</t>
         </is>
       </c>
       <c r="G331" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B332" s="29" t="inlineStr">
@@ -13453,24 +13453,24 @@
       <c r="D332" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E332" s="40" t="n">
-        <v>5</v>
+      <c r="E332" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F332" s="33" t="inlineStr">
         <is>
-          <t>Sweeney supervoting control; Tencent stake complexity</t>
+          <t>Clean structure; founder-led</t>
         </is>
       </c>
       <c r="G332" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B333" s="29" t="inlineStr">
@@ -13487,23 +13487,23 @@
         <v>0.2</v>
       </c>
       <c r="E333" s="42" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F333" s="33" t="inlineStr">
         <is>
-          <t>CFO w/ public-co experience; mature finance org</t>
+          <t>Profitable; audit-capable; no S-1</t>
         </is>
       </c>
       <c r="G333" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B334" s="29" t="inlineStr">
@@ -13519,24 +13519,24 @@
       <c r="D334" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E334" s="42" t="n">
-        <v>6</v>
+      <c r="E334" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F334" s="33" t="inlineStr">
         <is>
-          <t>Ongoing app-store antitrust litigation (mostly offensive)</t>
+          <t>Defense/ITAR posture; no material litigation</t>
         </is>
       </c>
       <c r="G334" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B335" s="29" t="inlineStr">
@@ -13553,11 +13553,11 @@
         <v>0.15</v>
       </c>
       <c r="E335" s="42" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F335" s="33" t="inlineStr">
         <is>
-          <t>Founder-led (Sweeney) 30+ yrs; stable</t>
+          <t>Stable founders (Younis/Chen ex-Google)</t>
         </is>
       </c>
       <c r="G335" s="31" t="inlineStr">
@@ -13576,7 +13576,7 @@
       <c r="C336" s="37" t="n"/>
       <c r="D336" s="37" t="n"/>
       <c r="E336" s="39" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="F336" s="37" t="n"/>
       <c r="G336" s="37" t="n"/>
@@ -13584,7 +13584,7 @@
     <row r="337">
       <c r="A337" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B337" s="29" t="inlineStr">
@@ -13600,12 +13600,12 @@
       <c r="D337" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E337" s="36" t="n">
-        <v>7.5</v>
+      <c r="E337" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F337" s="33" t="inlineStr">
         <is>
-          <t>Unreal Engine is category-leading tech; strong lead</t>
+          <t>Specialized autonomy/sim IP; strong but self-measured (cap)</t>
         </is>
       </c>
       <c r="G337" s="31" t="inlineStr">
@@ -13617,7 +13617,7 @@
     <row r="338">
       <c r="A338" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B338" s="29" t="inlineStr">
@@ -13633,12 +13633,12 @@
       <c r="D338" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E338" s="42" t="n">
-        <v>7</v>
+      <c r="E338" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F338" s="33" t="inlineStr">
         <is>
-          <t>Engine lock-in + content pipeline switching cost</t>
+          <t>Deep OEM toolchain integration = high switching cost</t>
         </is>
       </c>
       <c r="G338" s="31" t="inlineStr">
@@ -13650,7 +13650,7 @@
     <row r="339">
       <c r="A339" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B339" s="29" t="inlineStr">
@@ -13667,11 +13667,11 @@
         <v>0.2</v>
       </c>
       <c r="E339" s="42" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F339" s="33" t="inlineStr">
         <is>
-          <t>Retains top engine/graphics talent</t>
+          <t>Elite autonomy/robotics talent</t>
         </is>
       </c>
       <c r="G339" s="31" t="inlineStr">
@@ -13683,7 +13683,7 @@
     <row r="340">
       <c r="A340" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B340" s="29" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F340" s="33" t="inlineStr">
         <is>
-          <t>Fortnite/UEFN creator network effects</t>
+          <t>Proprietary driving-scenario datasets</t>
         </is>
       </c>
       <c r="G340" s="31" t="inlineStr">
@@ -13716,7 +13716,7 @@
     <row r="341">
       <c r="A341" s="28" t="inlineStr">
         <is>
-          <t>Epic Games</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="B341" s="29" t="inlineStr">
@@ -13733,11 +13733,11 @@
         <v>0.15</v>
       </c>
       <c r="E341" s="36" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F341" s="33" t="inlineStr">
         <is>
-          <t>Iconic global brand (Fortnite/Unreal)</t>
+          <t>Leading AV-simulation brand</t>
         </is>
       </c>
       <c r="G341" s="31" t="inlineStr">
@@ -13756,7 +13756,7 @@
       <c r="C342" s="37" t="n"/>
       <c r="D342" s="37" t="n"/>
       <c r="E342" s="39" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="F342" s="37" t="n"/>
       <c r="G342" s="37" t="n"/>
@@ -13765,17 +13765,17 @@
       <c r="A343" s="37" t="n"/>
       <c r="B343" s="44" t="inlineStr">
         <is>
-          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.5)</t>
+          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.25)</t>
         </is>
       </c>
       <c r="C343" s="37" t="n"/>
       <c r="D343" s="37" t="n"/>
       <c r="E343" s="47" t="n">
-        <v>6.89</v>
+        <v>6.91</v>
       </c>
       <c r="F343" s="46" t="inlineStr">
         <is>
-          <t>Tier: Strong   ·   Confidence ±3.75   ·   CRA weak-dims=0</t>
+          <t>Tier: Strong   ·   Confidence ±3.25   ·   CRA weak-dims=0</t>
         </is>
       </c>
       <c r="G343" s="37" t="n"/>
@@ -13783,7 +13783,7 @@
     <row r="345">
       <c r="A345" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B345" s="29" t="inlineStr">
@@ -13799,24 +13799,24 @@
       <c r="D345" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E345" s="41" t="n">
-        <v>3</v>
+      <c r="E345" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F345" s="33" t="inlineStr">
         <is>
-          <t>S5 EI gate fails (not FCF+; training losses); fallback S5-Bessemer low — massive net burn vs net-new</t>
+          <t>S5: profitable at times but Fortnite-cyclical; treat as mid Bessemer/EI</t>
         </is>
       </c>
       <c r="G345" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B346" s="29" t="inlineStr">
@@ -13832,24 +13832,24 @@
       <c r="D346" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E346" s="40" t="n">
-        <v>4</v>
+      <c r="E346" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F346" s="33" t="inlineStr">
         <is>
-          <t>GM ~40% (below AI-INFRA &gt;50% bonus threshold); improving to 63%E</t>
+          <t>Blended GM pressured by store rev-share payouts</t>
         </is>
       </c>
       <c r="G346" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B347" s="29" t="inlineStr">
@@ -13866,11 +13866,11 @@
         <v>0.2</v>
       </c>
       <c r="E347" s="42" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F347" s="33" t="inlineStr">
         <is>
-          <t>Burn trajectory improving; Q2 first operating profit</t>
+          <t>Post-2023 layoffs improved burn; stabilized</t>
         </is>
       </c>
       <c r="G347" s="31" t="inlineStr">
@@ -13882,7 +13882,7 @@
     <row r="348">
       <c r="A348" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B348" s="29" t="inlineStr">
@@ -13898,17 +13898,17 @@
       <c r="D348" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E348" s="40" t="n">
-        <v>4</v>
+      <c r="E348" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F348" s="33" t="inlineStr">
         <is>
-          <t>$124.3B equity + $37B debt; heavy dilution/leverage</t>
+          <t>Disney capital; modest dilution; strong cash gen</t>
         </is>
       </c>
       <c r="G348" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       <c r="C349" s="37" t="n"/>
       <c r="D349" s="37" t="n"/>
       <c r="E349" s="39" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="F349" s="37" t="n"/>
       <c r="G349" s="37" t="n"/>
@@ -13930,7 +13930,7 @@
     <row r="350">
       <c r="A350" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B350" s="29" t="inlineStr">
@@ -13946,24 +13946,24 @@
       <c r="D350" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E350" s="36" t="n">
-        <v>9</v>
+      <c r="E350" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F350" s="33" t="inlineStr">
         <is>
-          <t>NRR 140%+</t>
+          <t>Consumer bookings volatile with Fortnite seasonality (no classic NRR)</t>
         </is>
       </c>
       <c r="G350" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B351" s="29" t="inlineStr">
@@ -13979,24 +13979,24 @@
       <c r="D351" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E351" s="40" t="n">
-        <v>5</v>
+      <c r="E351" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F351" s="33" t="inlineStr">
         <is>
-          <t>Cloud-partner reseller concentration; Amazon/Google both investors+partners (-1.0 modifier applies)</t>
+          <t>Fortnite is a large share of bookings -&gt; title concentration</t>
         </is>
       </c>
       <c r="G351" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B352" s="29" t="inlineStr">
@@ -14012,24 +14012,24 @@
       <c r="D352" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E352" s="36" t="n">
-        <v>9</v>
+      <c r="E352" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F352" s="33" t="inlineStr">
         <is>
-          <t>~80% enterprise; 1,000+ at $1M+ ACV; deep F500</t>
+          <t>Unreal Engine enterprise licensing broadens base</t>
         </is>
       </c>
       <c r="G352" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B353" s="29" t="inlineStr">
@@ -14045,12 +14045,12 @@
       <c r="D353" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E353" s="36" t="n">
-        <v>7.5</v>
+      <c r="E353" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F353" s="33" t="inlineStr">
         <is>
-          <t>Growing committed enterprise contracts</t>
+          <t>Limited committed/recurring; transactional</t>
         </is>
       </c>
       <c r="G353" s="31" t="inlineStr">
@@ -14062,7 +14062,7 @@
     <row r="354">
       <c r="A354" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B354" s="29" t="inlineStr">
@@ -14078,17 +14078,17 @@
       <c r="D354" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E354" s="36" t="n">
-        <v>7.5</v>
+      <c r="E354" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F354" s="33" t="inlineStr">
         <is>
-          <t>Maintained per-token value; Opus pricing power</t>
+          <t>Pricing power in Unreal; store 12% take undercuts rivals</t>
         </is>
       </c>
       <c r="G354" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       <c r="C355" s="37" t="n"/>
       <c r="D355" s="37" t="n"/>
       <c r="E355" s="39" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="F355" s="37" t="n"/>
       <c r="G355" s="37" t="n"/>
@@ -14110,94 +14110,94 @@
     <row r="356">
       <c r="A356" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B356" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C356" s="31" t="inlineStr">
         <is>
-          <t>CI-1</t>
+          <t>SV-1</t>
         </is>
       </c>
       <c r="D356" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E356" s="40" t="n">
-        <v>4</v>
+      <c r="E356" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F356" s="33" t="inlineStr">
         <is>
-          <t>Multi-provider (AWS Trainium, Google TPU, SpaceX Colossus) but rents all training compute</t>
+          <t>Steady Unreal/Fortnite/UEFN releases</t>
         </is>
       </c>
       <c r="G356" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B357" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C357" s="31" t="inlineStr">
         <is>
-          <t>CI-2</t>
+          <t>SV-2</t>
         </is>
       </c>
       <c r="D357" s="31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E357" s="41" t="n">
-        <v>3</v>
+        <v>0.2</v>
+      </c>
+      <c r="E357" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F357" s="33" t="inlineStr">
         <is>
-          <t>No owned DC/fab; buys Alphabet-designed chips (debt-financed)</t>
+          <t>Global consumer footprint</t>
         </is>
       </c>
       <c r="G357" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B358" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C358" s="31" t="inlineStr">
         <is>
-          <t>CI-3</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="D358" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E358" s="41" t="n">
-        <v>3</v>
+        <v>0.25</v>
+      </c>
+      <c r="E358" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F358" s="33" t="inlineStr">
         <is>
-          <t>No owned power/PPA</t>
+          <t>Unreal ecosystem, marketplace, huge dev integrations</t>
         </is>
       </c>
       <c r="G358" s="31" t="inlineStr">
@@ -14209,66 +14209,66 @@
     <row r="359">
       <c r="A359" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B359" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C359" s="31" t="inlineStr">
         <is>
-          <t>CI-4</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="D359" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E359" s="40" t="n">
-        <v>4.5</v>
+      <c r="E359" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F359" s="33" t="inlineStr">
         <is>
-          <t>Diversifies silicon (Trainium/TPU/GPU) — less TSMC-single-point</t>
+          <t>Acquisitive (Bandcamp hist., Fab, Loci, Meshcapade)</t>
         </is>
       </c>
       <c r="G359" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B360" s="29" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)</t>
+          <t>Strategic Velocity (15%)</t>
         </is>
       </c>
       <c r="C360" s="31" t="inlineStr">
         <is>
-          <t>CI-5</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="D360" s="31" t="n">
         <v>0.1</v>
       </c>
       <c r="E360" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F360" s="33" t="inlineStr">
         <is>
-          <t>Colossus 90-day termination, retains all IP</t>
+          <t>Engine tech leadership</t>
         </is>
       </c>
       <c r="G360" s="31" t="inlineStr">
         <is>
-          <t>SEC(T1)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
@@ -14276,13 +14276,13 @@
       <c r="A361" s="37" t="n"/>
       <c r="B361" s="38" t="inlineStr">
         <is>
-          <t>Compute Independence (15%)  →  Dimension score</t>
+          <t>Strategic Velocity (15%)  →  Dimension score</t>
         </is>
       </c>
       <c r="C361" s="37" t="n"/>
       <c r="D361" s="37" t="n"/>
       <c r="E361" s="39" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="F361" s="37" t="n"/>
       <c r="G361" s="37" t="n"/>
@@ -14290,7 +14290,7 @@
     <row r="362">
       <c r="A362" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B362" s="29" t="inlineStr">
@@ -14306,24 +14306,24 @@
       <c r="D362" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E362" s="42" t="n">
-        <v>6.5</v>
+      <c r="E362" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F362" s="33" t="inlineStr">
         <is>
-          <t>LTBT + independent directors; S-1 governance maturing</t>
+          <t>Tencent ~40% + founder control; limited independence</t>
         </is>
       </c>
       <c r="G362" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B363" s="29" t="inlineStr">
@@ -14339,24 +14339,24 @@
       <c r="D363" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E363" s="42" t="n">
-        <v>6</v>
+      <c r="E363" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="F363" s="33" t="inlineStr">
         <is>
-          <t>PBC + Long-Term Benefit Trust; complex but disclosed</t>
+          <t>Sweeney supervoting control; Tencent stake complexity</t>
         </is>
       </c>
       <c r="G363" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B364" s="29" t="inlineStr">
@@ -14373,11 +14373,11 @@
         <v>0.2</v>
       </c>
       <c r="E364" s="42" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F364" s="33" t="inlineStr">
         <is>
-          <t>Confidential S-1 filed; bankers engaged; audit-grade</t>
+          <t>CFO w/ public-co experience; mature finance org</t>
         </is>
       </c>
       <c r="G364" s="31" t="inlineStr">
@@ -14389,7 +14389,7 @@
     <row r="365">
       <c r="A365" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B365" s="29" t="inlineStr">
@@ -14406,23 +14406,23 @@
         <v>0.2</v>
       </c>
       <c r="E365" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F365" s="33" t="inlineStr">
         <is>
-          <t>Copyright suits (industry-wide) but manageable; strong safety posture</t>
+          <t>Ongoing app-store antitrust litigation (mostly offensive)</t>
         </is>
       </c>
       <c r="G365" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B366" s="29" t="inlineStr">
@@ -14438,12 +14438,12 @@
       <c r="D366" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E366" s="36" t="n">
-        <v>7.5</v>
+      <c r="E366" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F366" s="33" t="inlineStr">
         <is>
-          <t>Stable founder team (Amodei); deep research bench</t>
+          <t>Founder-led (Sweeney) 30+ yrs; stable</t>
         </is>
       </c>
       <c r="G366" s="31" t="inlineStr">
@@ -14462,7 +14462,7 @@
       <c r="C367" s="37" t="n"/>
       <c r="D367" s="37" t="n"/>
       <c r="E367" s="39" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="F367" s="37" t="n"/>
       <c r="G367" s="37" t="n"/>
@@ -14470,7 +14470,7 @@
     <row r="368">
       <c r="A368" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B368" s="29" t="inlineStr">
@@ -14487,23 +14487,23 @@
         <v>0.25</v>
       </c>
       <c r="E368" s="36" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F368" s="33" t="inlineStr">
         <is>
-          <t>Frontier benchmark leadership (Opus 4.8 agentic lead) — but many self-published (cap direction-high/magnitude-low)</t>
+          <t>Unreal Engine is category-leading tech; strong lead</t>
         </is>
       </c>
       <c r="G368" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B369" s="29" t="inlineStr">
@@ -14519,12 +14519,12 @@
       <c r="D369" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E369" s="36" t="n">
-        <v>7.5</v>
+      <c r="E369" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F369" s="33" t="inlineStr">
         <is>
-          <t>Enterprise/API + Claude Code embedding; some switching cost</t>
+          <t>Engine lock-in + content pipeline switching cost</t>
         </is>
       </c>
       <c r="G369" s="31" t="inlineStr">
@@ -14536,7 +14536,7 @@
     <row r="370">
       <c r="A370" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B370" s="29" t="inlineStr">
@@ -14552,24 +14552,24 @@
       <c r="D370" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E370" s="36" t="n">
-        <v>8</v>
+      <c r="E370" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F370" s="33" t="inlineStr">
         <is>
-          <t>Elite research talent; net hires from rivals</t>
+          <t>Retains top engine/graphics talent</t>
         </is>
       </c>
       <c r="G370" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B371" s="29" t="inlineStr">
@@ -14585,12 +14585,12 @@
       <c r="D371" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E371" s="36" t="n">
-        <v>8</v>
+      <c r="E371" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F371" s="33" t="inlineStr">
         <is>
-          <t>Proprietary RLHF/safety data + Claude Code usage flywheel</t>
+          <t>Fortnite/UEFN creator network effects</t>
         </is>
       </c>
       <c r="G371" s="31" t="inlineStr">
@@ -14602,7 +14602,7 @@
     <row r="372">
       <c r="A372" s="28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Epic Games</t>
         </is>
       </c>
       <c r="B372" s="29" t="inlineStr">
@@ -14623,12 +14623,12 @@
       </c>
       <c r="F372" s="33" t="inlineStr">
         <is>
-          <t>Top-tier brand; ~54% coding share</t>
+          <t>Iconic global brand (Fortnite/Unreal)</t>
         </is>
       </c>
       <c r="G372" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       <c r="C373" s="37" t="n"/>
       <c r="D373" s="37" t="n"/>
       <c r="E373" s="39" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="F373" s="37" t="n"/>
       <c r="G373" s="37" t="n"/>
@@ -14657,11 +14657,11 @@
       <c r="C374" s="37" t="n"/>
       <c r="D374" s="37" t="n"/>
       <c r="E374" s="47" t="n">
-        <v>6.82</v>
+        <v>6.89</v>
       </c>
       <c r="F374" s="46" t="inlineStr">
         <is>
-          <t>Tier: Strong   ·   Confidence ±2.75   ·   CRA weak-dims=0</t>
+          <t>Tier: Strong   ·   Confidence ±3.75   ·   CRA weak-dims=0</t>
         </is>
       </c>
       <c r="G374" s="37" t="n"/>
@@ -16441,7 +16441,7 @@
     <row r="438">
       <c r="A438" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B438" s="29" t="inlineStr">
@@ -16457,12 +16457,12 @@
       <c r="D438" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E438" s="36" t="n">
-        <v>8.5</v>
+      <c r="E438" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F438" s="33" t="inlineStr">
         <is>
-          <t>S4 Bessemer: explosive net-new ARR ($2B-&gt;$4B in ~4mo) on small team/burn</t>
+          <t>S5 EI gate fails -&gt; fix#2 Bessemer fallback: net-new ARR ~$15B vs ~$21B net burn ~=0.7x = moderately growth-efficient; absolute-loss/obligations sit in CE-2/CE-4</t>
         </is>
       </c>
       <c r="G438" s="31" t="inlineStr">
@@ -16474,7 +16474,7 @@
     <row r="439">
       <c r="A439" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B439" s="29" t="inlineStr">
@@ -16490,24 +16490,24 @@
       <c r="D439" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E439" s="40" t="n">
-        <v>4</v>
+      <c r="E439" s="41" t="n">
+        <v>2.5</v>
       </c>
       <c r="F439" s="33" t="inlineStr">
         <is>
-          <t>GM compressed (~30-50%) — pays frontier-model inference COGS; AI-APP no infra bonus</t>
+          <t>2025 GM 33% — well below AI-INFRA &gt;50% bonus; below peer</t>
         </is>
       </c>
       <c r="G439" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B440" s="29" t="inlineStr">
@@ -16523,24 +16523,24 @@
       <c r="D440" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E440" s="36" t="n">
-        <v>8</v>
+      <c r="E440" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F440" s="33" t="inlineStr">
         <is>
-          <t>Revenue scaling far faster than burn</t>
+          <t>Burn still enormous; some improvement but FCF trough ahead</t>
         </is>
       </c>
       <c r="G440" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B441" s="29" t="inlineStr">
@@ -16556,17 +16556,17 @@
       <c r="D441" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E441" s="36" t="n">
-        <v>7.5</v>
+      <c r="E441" s="41" t="n">
+        <v>2.5</v>
       </c>
       <c r="F441" s="33" t="inlineStr">
         <is>
-          <t>$3.4B raised, tiny headcount; near-acquisition liquidity</t>
+          <t>$181.2B equity raised (heaviest dilution) + $1.15T obligations</t>
         </is>
       </c>
       <c r="G441" s="31" t="inlineStr">
         <is>
-          <t>PB(T2)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16580,7 @@
       <c r="C442" s="37" t="n"/>
       <c r="D442" s="37" t="n"/>
       <c r="E442" s="39" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="F442" s="37" t="n"/>
       <c r="G442" s="37" t="n"/>
@@ -16588,7 +16588,7 @@
     <row r="443">
       <c r="A443" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B443" s="29" t="inlineStr">
@@ -16604,24 +16604,24 @@
       <c r="D443" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E443" s="42" t="n">
-        <v>7</v>
+      <c r="E443" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F443" s="33" t="inlineStr">
         <is>
-          <t>High expansion but consumer/seat churn risk in hot category</t>
+          <t>Strong consumer + enterprise expansion; some consumer churn</t>
         </is>
       </c>
       <c r="G443" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B444" s="29" t="inlineStr">
@@ -16642,19 +16642,19 @@
       </c>
       <c r="F444" s="33" t="inlineStr">
         <is>
-          <t>Broadening enterprise (~$2.6B) reduces concentration; supplier (Anthropic) not investor-customer</t>
+          <t>Microsoft partner+investor concentration (revenue-share coupling)</t>
         </is>
       </c>
       <c r="G444" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T2)</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B445" s="29" t="inlineStr">
@@ -16670,12 +16670,12 @@
       <c r="D445" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E445" s="42" t="n">
-        <v>7</v>
+      <c r="E445" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F445" s="33" t="inlineStr">
         <is>
-          <t>Fast enterprise adoption; many dev-team seats</t>
+          <t>Enterprise &gt;40% and rising; huge logo base</t>
         </is>
       </c>
       <c r="G445" s="31" t="inlineStr">
@@ -16687,7 +16687,7 @@
     <row r="446">
       <c r="A446" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B446" s="29" t="inlineStr">
@@ -16703,12 +16703,12 @@
       <c r="D446" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E446" s="40" t="n">
-        <v>5.5</v>
+      <c r="E446" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F446" s="33" t="inlineStr">
         <is>
-          <t>Mostly monthly/seat; limited multi-year committed</t>
+          <t>Growing committed enterprise; consumer largely monthly</t>
         </is>
       </c>
       <c r="G446" s="31" t="inlineStr">
@@ -16720,7 +16720,7 @@
     <row r="447">
       <c r="A447" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B447" s="29" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="F447" s="33" t="inlineStr">
         <is>
-          <t>Pricing power strong now; compute-cost pass-through risk</t>
+          <t>Pricing power but aggressive price competition (self-inflicted)</t>
         </is>
       </c>
       <c r="G447" s="31" t="inlineStr">
@@ -16760,7 +16760,7 @@
       <c r="C448" s="37" t="n"/>
       <c r="D448" s="37" t="n"/>
       <c r="E448" s="39" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="F448" s="37" t="n"/>
       <c r="G448" s="37" t="n"/>
@@ -16768,7 +16768,7 @@
     <row r="449">
       <c r="A449" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B449" s="29" t="inlineStr">
@@ -16784,24 +16784,24 @@
       <c r="D449" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E449" s="41" t="n">
-        <v>2.5</v>
+      <c r="E449" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F449" s="33" t="inlineStr">
         <is>
-          <t>Near-total dependence on external frontier-model providers (Anthropic/OpenAI)</t>
+          <t>Heavy Microsoft/Azure but now multi-provider (Oracle/CoreWeave + Stargate build-out) reduces single-provider share</t>
         </is>
       </c>
       <c r="G449" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B450" s="29" t="inlineStr">
@@ -16818,23 +16818,23 @@
         <v>0.25</v>
       </c>
       <c r="E450" s="41" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F450" s="33" t="inlineStr">
         <is>
-          <t>No owned DC/compute/silicon</t>
+          <t>Stargate build-out toward owned capacity but not yet operational scale</t>
         </is>
       </c>
       <c r="G450" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B451" s="29" t="inlineStr">
@@ -16851,11 +16851,11 @@
         <v>0.2</v>
       </c>
       <c r="E451" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F451" s="33" t="inlineStr">
         <is>
-          <t>No owned power</t>
+          <t>No owned power at scale yet</t>
         </is>
       </c>
       <c r="G451" s="31" t="inlineStr">
@@ -16867,7 +16867,7 @@
     <row r="452">
       <c r="A452" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B452" s="29" t="inlineStr">
@@ -16883,24 +16883,24 @@
       <c r="D452" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E452" s="41" t="n">
-        <v>3</v>
+      <c r="E452" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F452" s="33" t="inlineStr">
         <is>
-          <t>Indirect NVIDIA exposure via providers</t>
+          <t>NVIDIA-heavy; exploring custom silicon (Broadcom)</t>
         </is>
       </c>
       <c r="G452" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B453" s="29" t="inlineStr">
@@ -16916,17 +16916,17 @@
       <c r="D453" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="E453" s="41" t="n">
-        <v>3</v>
+      <c r="E453" s="40" t="n">
+        <v>4.5</v>
       </c>
       <c r="F453" s="33" t="inlineStr">
         <is>
-          <t>No exclusivity protections; model-supplier competition risk (both build rival tools)</t>
+          <t>MSFT relationship easing exclusivity; $1.15T commitments lock-in</t>
         </is>
       </c>
       <c r="G453" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
@@ -16940,19 +16940,15 @@
       <c r="C454" s="37" t="n"/>
       <c r="D454" s="37" t="n"/>
       <c r="E454" s="39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F454" s="43" t="inlineStr">
-        <is>
-          <t>AI-APP CI 10% / MD 25%</t>
-        </is>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="F454" s="37" t="n"/>
       <c r="G454" s="37" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B455" s="29" t="inlineStr">
@@ -16969,23 +16965,23 @@
         <v>0.25</v>
       </c>
       <c r="E455" s="40" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F455" s="33" t="inlineStr">
         <is>
-          <t>Young founder board; being absorbed into SpaceX governance</t>
+          <t>Board rebuilt post-2023; independents added</t>
         </is>
       </c>
       <c r="G455" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B456" s="29" t="inlineStr">
@@ -17001,24 +16997,24 @@
       <c r="D456" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E456" s="40" t="n">
-        <v>4.5</v>
+      <c r="E456" s="41" t="n">
+        <v>2</v>
       </c>
       <c r="F456" s="33" t="inlineStr">
         <is>
-          <t>All-stock takeout by SpaceX -&gt; minority in Musk-controlled entity</t>
+          <t>Nonprofit-&gt;PBC conversion incomplete (-1.0 modifier); Altman Co-CEO ambiguity</t>
         </is>
       </c>
       <c r="G456" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B457" s="29" t="inlineStr">
@@ -17034,24 +17030,24 @@
       <c r="D457" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E457" s="40" t="n">
-        <v>4</v>
+      <c r="E457" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F457" s="33" t="inlineStr">
         <is>
-          <t>No standalone audited financials/S-1</t>
+          <t>Confidential S-1; audited FY2025; bankers engaged</t>
         </is>
       </c>
       <c r="G457" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B458" s="29" t="inlineStr">
@@ -17068,23 +17064,23 @@
         <v>0.2</v>
       </c>
       <c r="E458" s="40" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F458" s="33" t="inlineStr">
         <is>
-          <t>Publisher/IP-scraping and code-license risk emerging</t>
+          <t>Musk litigation; copyright suits; regulatory scrutiny</t>
         </is>
       </c>
       <c r="G458" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B459" s="29" t="inlineStr">
@@ -17101,16 +17097,16 @@
         <v>0.15</v>
       </c>
       <c r="E459" s="40" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F459" s="33" t="inlineStr">
         <is>
-          <t>Very young leadership; key-person risk; acquisition transition</t>
+          <t>Altman stable but 2023 turmoil + exec departures history</t>
         </is>
       </c>
       <c r="G459" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
@@ -17124,7 +17120,7 @@
       <c r="C460" s="37" t="n"/>
       <c r="D460" s="37" t="n"/>
       <c r="E460" s="39" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F460" s="37" t="n"/>
       <c r="G460" s="37" t="n"/>
@@ -17132,7 +17128,7 @@
     <row r="461">
       <c r="A461" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B461" s="29" t="inlineStr">
@@ -17148,24 +17144,24 @@
       <c r="D461" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E461" s="42" t="n">
-        <v>6</v>
+      <c r="E461" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F461" s="33" t="inlineStr">
         <is>
-          <t>Product UX lead, but underlying intelligence is licensed (thin model moat) — cap</t>
+          <t>Frontier model leadership (GPT-5.x); benchmarks partly self-published (cap)</t>
         </is>
       </c>
       <c r="G461" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B462" s="29" t="inlineStr">
@@ -17181,12 +17177,12 @@
       <c r="D462" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E462" s="40" t="n">
-        <v>5.5</v>
+      <c r="E462" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F462" s="33" t="inlineStr">
         <is>
-          <t>Workflow/codebase embedding gives some switching cost; editors swap-able</t>
+          <t>ChatGPT habit + API/enterprise embedding</t>
         </is>
       </c>
       <c r="G462" s="31" t="inlineStr">
@@ -17198,7 +17194,7 @@
     <row r="463">
       <c r="A463" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B463" s="29" t="inlineStr">
@@ -17215,23 +17211,23 @@
         <v>0.2</v>
       </c>
       <c r="E463" s="42" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F463" s="33" t="inlineStr">
         <is>
-          <t>Elite eng talent; retention aided by upside</t>
+          <t>Elite research talent but notable departures (safety exits)</t>
         </is>
       </c>
       <c r="G463" s="31" t="inlineStr">
         <is>
-          <t>Est(T4)</t>
+          <t>Canonical(T3)</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B464" s="29" t="inlineStr">
@@ -17247,12 +17243,12 @@
       <c r="D464" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E464" s="42" t="n">
-        <v>6.5</v>
+      <c r="E464" s="36" t="n">
+        <v>8.5</v>
       </c>
       <c r="F464" s="33" t="inlineStr">
         <is>
-          <t>Proprietary code-interaction data flywheel growing</t>
+          <t>900M WAU consumer-scale data flywheel (largest)</t>
         </is>
       </c>
       <c r="G464" s="31" t="inlineStr">
@@ -17264,7 +17260,7 @@
     <row r="465">
       <c r="A465" s="28" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B465" s="29" t="inlineStr">
@@ -17281,11 +17277,11 @@
         <v>0.15</v>
       </c>
       <c r="E465" s="36" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="F465" s="33" t="inlineStr">
         <is>
-          <t>Dominant brand in AI coding (fastest to $1B ARR)</t>
+          <t>ChatGPT = iconic global AI brand (category-defining)</t>
         </is>
       </c>
       <c r="G465" s="31" t="inlineStr">
@@ -17304,7 +17300,7 @@
       <c r="C466" s="37" t="n"/>
       <c r="D466" s="37" t="n"/>
       <c r="E466" s="39" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="F466" s="37" t="n"/>
       <c r="G466" s="37" t="n"/>
@@ -17313,17 +17309,17 @@
       <c r="A467" s="37" t="n"/>
       <c r="B467" s="44" t="inlineStr">
         <is>
-          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.25)</t>
+          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.5)</t>
         </is>
       </c>
       <c r="C467" s="37" t="n"/>
       <c r="D467" s="37" t="n"/>
       <c r="E467" s="48" t="n">
-        <v>6.05</v>
+        <v>6.3</v>
       </c>
       <c r="F467" s="46" t="inlineStr">
         <is>
-          <t>Tier: Developing   ·   Confidence ±3.25   ·   CRA weak-dims=1</t>
+          <t>Tier: Developing   ·   Confidence ±2.75   ·   CRA weak-dims=0</t>
         </is>
       </c>
       <c r="G467" s="37" t="n"/>
@@ -17331,7 +17327,7 @@
     <row r="469">
       <c r="A469" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B469" s="29" t="inlineStr">
@@ -17347,12 +17343,12 @@
       <c r="D469" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E469" s="41" t="n">
-        <v>3</v>
+      <c r="E469" s="36" t="n">
+        <v>8.5</v>
       </c>
       <c r="F469" s="33" t="inlineStr">
         <is>
-          <t>S5 EI gate fails (deep losses); fallback S5-Bessemer very low — ~$20B+ op loss vs net-new</t>
+          <t>S4 Bessemer: explosive net-new ARR ($2B-&gt;$4B in ~4mo) on small team/burn</t>
         </is>
       </c>
       <c r="G469" s="31" t="inlineStr">
@@ -17364,7 +17360,7 @@
     <row r="470">
       <c r="A470" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B470" s="29" t="inlineStr">
@@ -17380,24 +17376,24 @@
       <c r="D470" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E470" s="41" t="n">
-        <v>2.5</v>
+      <c r="E470" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F470" s="33" t="inlineStr">
         <is>
-          <t>2025 GM 33% — well below AI-INFRA &gt;50% bonus; below peer</t>
+          <t>GM compressed (~30-50%) — pays frontier-model inference COGS; AI-APP no infra bonus</t>
         </is>
       </c>
       <c r="G470" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B471" s="29" t="inlineStr">
@@ -17413,24 +17409,24 @@
       <c r="D471" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E471" s="40" t="n">
-        <v>5.5</v>
+      <c r="E471" s="36" t="n">
+        <v>8</v>
       </c>
       <c r="F471" s="33" t="inlineStr">
         <is>
-          <t>Burn still enormous; some improvement but FCF trough ahead</t>
+          <t>Revenue scaling far faster than burn</t>
         </is>
       </c>
       <c r="G471" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B472" s="29" t="inlineStr">
@@ -17446,17 +17442,17 @@
       <c r="D472" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E472" s="41" t="n">
-        <v>2.5</v>
+      <c r="E472" s="36" t="n">
+        <v>7.5</v>
       </c>
       <c r="F472" s="33" t="inlineStr">
         <is>
-          <t>$181.2B equity raised (heaviest dilution) + $1.15T obligations</t>
+          <t>$3.4B raised, tiny headcount; near-acquisition liquidity</t>
         </is>
       </c>
       <c r="G472" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>PB(T2)</t>
         </is>
       </c>
     </row>
@@ -17470,7 +17466,7 @@
       <c r="C473" s="37" t="n"/>
       <c r="D473" s="37" t="n"/>
       <c r="E473" s="39" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="F473" s="37" t="n"/>
       <c r="G473" s="37" t="n"/>
@@ -17478,7 +17474,7 @@
     <row r="474">
       <c r="A474" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B474" s="29" t="inlineStr">
@@ -17494,24 +17490,24 @@
       <c r="D474" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E474" s="36" t="n">
-        <v>7.5</v>
+      <c r="E474" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F474" s="33" t="inlineStr">
         <is>
-          <t>Strong consumer + enterprise expansion; some consumer churn</t>
+          <t>High expansion but consumer/seat churn risk in hot category</t>
         </is>
       </c>
       <c r="G474" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B475" s="29" t="inlineStr">
@@ -17532,19 +17528,19 @@
       </c>
       <c r="F475" s="33" t="inlineStr">
         <is>
-          <t>Microsoft partner+investor concentration (revenue-share coupling)</t>
+          <t>Broadening enterprise (~$2.6B) reduces concentration; supplier (Anthropic) not investor-customer</t>
         </is>
       </c>
       <c r="G475" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T2)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B476" s="29" t="inlineStr">
@@ -17560,12 +17556,12 @@
       <c r="D476" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E476" s="36" t="n">
-        <v>7.5</v>
+      <c r="E476" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="F476" s="33" t="inlineStr">
         <is>
-          <t>Enterprise &gt;40% and rising; huge logo base</t>
+          <t>Fast enterprise adoption; many dev-team seats</t>
         </is>
       </c>
       <c r="G476" s="31" t="inlineStr">
@@ -17577,7 +17573,7 @@
     <row r="477">
       <c r="A477" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B477" s="29" t="inlineStr">
@@ -17593,12 +17589,12 @@
       <c r="D477" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E477" s="42" t="n">
-        <v>6</v>
+      <c r="E477" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F477" s="33" t="inlineStr">
         <is>
-          <t>Growing committed enterprise; consumer largely monthly</t>
+          <t>Mostly monthly/seat; limited multi-year committed</t>
         </is>
       </c>
       <c r="G477" s="31" t="inlineStr">
@@ -17610,7 +17606,7 @@
     <row r="478">
       <c r="A478" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B478" s="29" t="inlineStr">
@@ -17631,7 +17627,7 @@
       </c>
       <c r="F478" s="33" t="inlineStr">
         <is>
-          <t>Pricing power but aggressive price competition (self-inflicted)</t>
+          <t>Pricing power strong now; compute-cost pass-through risk</t>
         </is>
       </c>
       <c r="G478" s="31" t="inlineStr">
@@ -17650,7 +17646,7 @@
       <c r="C479" s="37" t="n"/>
       <c r="D479" s="37" t="n"/>
       <c r="E479" s="39" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="F479" s="37" t="n"/>
       <c r="G479" s="37" t="n"/>
@@ -17658,7 +17654,7 @@
     <row r="480">
       <c r="A480" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B480" s="29" t="inlineStr">
@@ -17675,23 +17671,23 @@
         <v>0.3</v>
       </c>
       <c r="E480" s="41" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F480" s="33" t="inlineStr">
         <is>
-          <t>Heavy Microsoft/Azure + Oracle/CoreWeave dependence; diversifying (Stargate)</t>
+          <t>Near-total dependence on external frontier-model providers (Anthropic/OpenAI)</t>
         </is>
       </c>
       <c r="G480" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B481" s="29" t="inlineStr">
@@ -17708,23 +17704,23 @@
         <v>0.25</v>
       </c>
       <c r="E481" s="41" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F481" s="33" t="inlineStr">
         <is>
-          <t>Stargate build-out toward owned capacity but not yet operational scale</t>
+          <t>No owned DC/compute/silicon</t>
         </is>
       </c>
       <c r="G481" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B482" s="29" t="inlineStr">
@@ -17741,11 +17737,11 @@
         <v>0.2</v>
       </c>
       <c r="E482" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F482" s="33" t="inlineStr">
         <is>
-          <t>No owned power at scale yet</t>
+          <t>No owned power</t>
         </is>
       </c>
       <c r="G482" s="31" t="inlineStr">
@@ -17757,7 +17753,7 @@
     <row r="483">
       <c r="A483" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B483" s="29" t="inlineStr">
@@ -17773,24 +17769,24 @@
       <c r="D483" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E483" s="40" t="n">
-        <v>4</v>
+      <c r="E483" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="F483" s="33" t="inlineStr">
         <is>
-          <t>NVIDIA-heavy; exploring custom silicon (Broadcom)</t>
+          <t>Indirect NVIDIA exposure via providers</t>
         </is>
       </c>
       <c r="G483" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B484" s="29" t="inlineStr">
@@ -17806,17 +17802,17 @@
       <c r="D484" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="E484" s="40" t="n">
-        <v>4.5</v>
+      <c r="E484" s="41" t="n">
+        <v>3</v>
       </c>
       <c r="F484" s="33" t="inlineStr">
         <is>
-          <t>MSFT relationship easing exclusivity; $1.15T commitments lock-in</t>
+          <t>No exclusivity protections; model-supplier competition risk (both build rival tools)</t>
         </is>
       </c>
       <c r="G484" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
@@ -17830,15 +17826,19 @@
       <c r="C485" s="37" t="n"/>
       <c r="D485" s="37" t="n"/>
       <c r="E485" s="39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F485" s="37" t="n"/>
+        <v>2.4</v>
+      </c>
+      <c r="F485" s="43" t="inlineStr">
+        <is>
+          <t>AI-APP CI 10% / MD 25%</t>
+        </is>
+      </c>
       <c r="G485" s="37" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B486" s="29" t="inlineStr">
@@ -17855,23 +17855,23 @@
         <v>0.25</v>
       </c>
       <c r="E486" s="40" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F486" s="33" t="inlineStr">
         <is>
-          <t>Board rebuilt post-2023; independents added</t>
+          <t>Young founder board; being absorbed into SpaceX governance</t>
         </is>
       </c>
       <c r="G486" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B487" s="29" t="inlineStr">
@@ -17887,24 +17887,24 @@
       <c r="D487" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E487" s="41" t="n">
-        <v>2</v>
+      <c r="E487" s="40" t="n">
+        <v>4.5</v>
       </c>
       <c r="F487" s="33" t="inlineStr">
         <is>
-          <t>Nonprofit-&gt;PBC conversion incomplete (-1.0 modifier); Altman Co-CEO ambiguity</t>
+          <t>All-stock takeout by SpaceX -&gt; minority in Musk-controlled entity</t>
         </is>
       </c>
       <c r="G487" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B488" s="29" t="inlineStr">
@@ -17920,24 +17920,24 @@
       <c r="D488" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E488" s="42" t="n">
-        <v>6.5</v>
+      <c r="E488" s="40" t="n">
+        <v>4</v>
       </c>
       <c r="F488" s="33" t="inlineStr">
         <is>
-          <t>Confidential S-1; audited FY2025; bankers engaged</t>
+          <t>No standalone audited financials/S-1</t>
         </is>
       </c>
       <c r="G488" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B489" s="29" t="inlineStr">
@@ -17954,23 +17954,23 @@
         <v>0.2</v>
       </c>
       <c r="E489" s="40" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F489" s="33" t="inlineStr">
         <is>
-          <t>Musk litigation; copyright suits; regulatory scrutiny</t>
+          <t>Publisher/IP-scraping and code-license risk emerging</t>
         </is>
       </c>
       <c r="G489" s="31" t="inlineStr">
         <is>
-          <t>Web(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B490" s="29" t="inlineStr">
@@ -17987,16 +17987,16 @@
         <v>0.15</v>
       </c>
       <c r="E490" s="40" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F490" s="33" t="inlineStr">
         <is>
-          <t>Altman stable but 2023 turmoil + exec departures history</t>
+          <t>Very young leadership; key-person risk; acquisition transition</t>
         </is>
       </c>
       <c r="G490" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18010,7 @@
       <c r="C491" s="37" t="n"/>
       <c r="D491" s="37" t="n"/>
       <c r="E491" s="39" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F491" s="37" t="n"/>
       <c r="G491" s="37" t="n"/>
@@ -18018,7 +18018,7 @@
     <row r="492">
       <c r="A492" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B492" s="29" t="inlineStr">
@@ -18034,24 +18034,24 @@
       <c r="D492" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E492" s="36" t="n">
-        <v>8</v>
+      <c r="E492" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="F492" s="33" t="inlineStr">
         <is>
-          <t>Frontier model leadership (GPT-5.x); benchmarks partly self-published (cap)</t>
+          <t>Product UX lead, but underlying intelligence is licensed (thin model moat) — cap</t>
         </is>
       </c>
       <c r="G492" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Web(T3)</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B493" s="29" t="inlineStr">
@@ -18067,12 +18067,12 @@
       <c r="D493" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E493" s="42" t="n">
-        <v>7</v>
+      <c r="E493" s="40" t="n">
+        <v>5.5</v>
       </c>
       <c r="F493" s="33" t="inlineStr">
         <is>
-          <t>ChatGPT habit + API/enterprise embedding</t>
+          <t>Workflow/codebase embedding gives some switching cost; editors swap-able</t>
         </is>
       </c>
       <c r="G493" s="31" t="inlineStr">
@@ -18084,7 +18084,7 @@
     <row r="494">
       <c r="A494" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B494" s="29" t="inlineStr">
@@ -18101,23 +18101,23 @@
         <v>0.2</v>
       </c>
       <c r="E494" s="42" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F494" s="33" t="inlineStr">
         <is>
-          <t>Elite research talent but notable departures (safety exits)</t>
+          <t>Elite eng talent; retention aided by upside</t>
         </is>
       </c>
       <c r="G494" s="31" t="inlineStr">
         <is>
-          <t>Canonical(T3)</t>
+          <t>Est(T4)</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B495" s="29" t="inlineStr">
@@ -18133,12 +18133,12 @@
       <c r="D495" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E495" s="36" t="n">
-        <v>8.5</v>
+      <c r="E495" s="42" t="n">
+        <v>6.5</v>
       </c>
       <c r="F495" s="33" t="inlineStr">
         <is>
-          <t>900M WAU consumer-scale data flywheel (largest)</t>
+          <t>Proprietary code-interaction data flywheel growing</t>
         </is>
       </c>
       <c r="G495" s="31" t="inlineStr">
@@ -18150,7 +18150,7 @@
     <row r="496">
       <c r="A496" s="28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B496" s="29" t="inlineStr">
@@ -18167,11 +18167,11 @@
         <v>0.15</v>
       </c>
       <c r="E496" s="36" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="F496" s="33" t="inlineStr">
         <is>
-          <t>ChatGPT = iconic global AI brand (category-defining)</t>
+          <t>Dominant brand in AI coding (fastest to $1B ARR)</t>
         </is>
       </c>
       <c r="G496" s="31" t="inlineStr">
@@ -18190,7 +18190,7 @@
       <c r="C497" s="37" t="n"/>
       <c r="D497" s="37" t="n"/>
       <c r="E497" s="39" t="n">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="F497" s="37" t="n"/>
       <c r="G497" s="37" t="n"/>
@@ -18199,17 +18199,17 @@
       <c r="A498" s="37" t="n"/>
       <c r="B498" s="44" t="inlineStr">
         <is>
-          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.5)</t>
+          <t>COMPOSITE = Σ(dim×w) − CRA(0.0) + StageAdj(0.25)</t>
         </is>
       </c>
       <c r="C498" s="37" t="n"/>
       <c r="D498" s="37" t="n"/>
       <c r="E498" s="48" t="n">
-        <v>5.96</v>
+        <v>6.05</v>
       </c>
       <c r="F498" s="46" t="inlineStr">
         <is>
-          <t>Tier: Developing   ·   Confidence ±2.75   ·   CRA weak-dims=0</t>
+          <t>Tier: Developing   ·   Confidence ±3.25   ·   CRA weak-dims=1</t>
         </is>
       </c>
       <c r="G498" s="37" t="n"/>
@@ -27348,7 +27348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J13"/>
+  <dimension ref="B2:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -27397,107 +27397,120 @@
     <row r="6" ht="58" customHeight="1">
       <c r="B6" s="55" t="inlineStr">
         <is>
-          <t>The frontier-lab paradox</t>
+          <t>REVISION v1.1 (CE-1 fallback)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Anthropic &amp; OpenAI are the two highest-valued names ($965B / $852B) yet score Developing — CE is punished (Anthropic CE-1=3 on training losses/40% GM; OpenAI CE-1=3, CE-2=2.5 on 33% GM + $1.15T obligations) and CI is structurally low (rent all compute). Quality (MD 8+) does not offset capital inefficiency in this framework.</t>
+          <t>Applied fix #2 consistently to the two S5 gate-failers: CE-1 now uses the Bessemer growth-efficiency fallback (net-new ARR / net burn), not an absolute-loss read. Anthropic CE-1 3-&gt;7.5 (~0.9-1.0x), OpenAI CE-1 3-&gt;7 (~0.7x). Absolute-loss/dilution concern remains in CE-2 (margin) + CE-4 (dilution/obligations), not double-counted in CE-1. Small fact-based CI-1 nudge (multi-provider diversification): Anthropic 4-&gt;5, OpenAI 3.5-&gt;4. Net: Anthropic 6.82-&gt;7.23 (Strong), OpenAI 5.96-&gt;6.30 (Developing). No other name affected (they pass the S5 gate or aren't S5).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>Anthropic vs OpenAI</t>
+          <t>The frontier-lab paradox</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Anthropic scores materially higher (GO-2: OpenAI −1.0 nonprofit→PBC conversion incomplete + Co-CEO ambiguity; Anthropic cleaner PBC/LTBT). Both flagged: revenue-basis mismatch (Anthropic GROSS $47B ≈ NET $28.3B; OpenAI NET $25B) — never compared raw (Ruling 5).</t>
+          <t>Anthropic &amp; OpenAI are the two highest-valued names ($965B / $852B) yet do NOT reach Elite — even after the CE-1 fix, CE-2 (Anthropic 40% GM / OpenAI 33% GM, no &gt;50% bonus) and CE-4 (heaviest dilution + OpenAI's $1.15T obligations) plus structurally low CI (rent all compute) hold them to Strong/Developing. The corrected read is more precise: these labs are growth-EFFICIENT (huge net-new ARR per burn dollar) but margin-poor and dilution-heavy. Quality (MD 8+) does not fully offset.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="B8" s="55" t="inlineStr">
         <is>
-          <t>Cerebras concentration bomb</t>
+          <t>Anthropic vs OpenAI</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>RQ-2 = 1.5: ~86% of 2025 revenue from UAE-related parties (G42 24% + MBZUAI 62%). Public (CBRS) lifts GO-3 to 8, but CFIUS/geopolitical overhang (GO-4=4.5) and TSMC single-foundry (CI-4=3.5, reweighted to 30%) cap it.</t>
+          <t>Anthropic scores materially higher (GO-2: OpenAI −1.0 nonprofit→PBC conversion incomplete + Co-CEO ambiguity; Anthropic cleaner PBC/LTBT). Both flagged: revenue-basis mismatch (Anthropic GROSS $47B ≈ NET $28.3B; OpenAI NET $25B) — never compared raw (Ruling 5).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="B9" s="55" t="inlineStr">
         <is>
-          <t>Deel vs Rippling litigation</t>
+          <t>Cerebras concentration bomb</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>GO-4 asymmetry: Deel = 2.5 (DOJ-investigated DEFENDANT in RICO/trade-secret suit); Rippling = 6.5 (PLAINTIFF, favorable posture but distraction). Same event, opposite sign.</t>
+          <t>RQ-2 = 1.5: ~86% of 2025 revenue from UAE-related parties (G42 24% + MBZUAI 62%). Public (CBRS) lifts GO-3 to 8, but CFIUS/geopolitical overhang (GO-4=4.5) and TSMC single-foundry (CI-4=3.5, reweighted to 30%) cap it.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="B10" s="55" t="inlineStr">
         <is>
-          <t>Cursor routing &amp; fragility</t>
+          <t>Deel vs Rippling litigation</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>AIBQ AI-APP but CI = ~2.2 (near-total dependence on Anthropic/OpenAI, who also build rival tools). ~$4B ARR at gross basis with compressed margins (CE-2=4). Being absorbed into SpaceX ($60B all-stock) — GO optionality shifts to a Musk-controlled entity.</t>
+          <t>GO-4 asymmetry: Deel = 2.5 (DOJ-investigated DEFENDANT in RICO/trade-secret suit); Rippling = 6.5 (PLAINTIFF, favorable posture but distraction). Same event, opposite sign.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="B11" s="55" t="inlineStr">
         <is>
-          <t>Freshness flags</t>
+          <t>Cursor routing &amp; fragility</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>No name fully disqualifies (&gt;365d), but stale-valuation flags: Epic ($22.5B, Nov-2024), Figure ($39B, May-2025), Neuralink ($9.65B, Jun-2025), Perplexity ($20B, Sep-2025). Composition effect: SPCX now public; Cursor &amp; Kraken in-motion (acquisition / IPO).</t>
+          <t>AIBQ AI-APP but CI = ~2.2 (near-total dependence on Anthropic/OpenAI, who also build rival tools). ~$4B ARR at gross basis with compressed margins (CE-2=4). Being absorbed into SpaceX ($60B all-stock) — GO optionality shifts to a Musk-controlled entity.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="B12" s="55" t="inlineStr">
         <is>
-          <t>Ruling-4 traps caught</t>
+          <t>Freshness flags</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>PitchBook 'TTM 4Qxx' revenue fields are FORWARD PROJECTIONS, excluded from stage/CE: Anthropic $55B(4Q2027!), OpenAI $30B, Ramp $1.5B, Databricks $6.9B, Cursor $6.0B, Perplexity $1.0B. Stage assigned on current actual run-rate instead.</t>
+          <t>No name fully disqualifies (&gt;365d), but stale-valuation flags: Epic ($22.5B, Nov-2024), Figure ($39B, May-2025), Neuralink ($9.65B, Jun-2025), Perplexity ($20B, Sep-2025). Composition effect: SPCX now public; Cursor &amp; Kraken in-motion (acquisition / IPO).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="B13" s="55" t="inlineStr">
         <is>
+          <t>Ruling-4 traps caught</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>PitchBook 'TTM 4Qxx' revenue fields are FORWARD PROJECTIONS, excluded from stage/CE: Anthropic $55B(4Q2027!), OpenAI $30B, Ramp $1.5B, Databricks $6.9B, Cursor $6.0B, Perplexity $1.0B. Stage assigned on current actual run-rate instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="B14" s="55" t="inlineStr">
+        <is>
           <t>Data-quality honesty</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Soft dimensions (GO, MD, and RQ where NRR/concentration undisclosed) are analyst anchor-matched (T4) and carry the ± band. Hard financials (valuation, raised, headcount, actual revenue) are PitchBook T2 or SEC T1. MD-1 capped wherever only self-published benchmarks exist.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="C7:J7"/>
     <mergeCell ref="C11:J11"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C14:J14"/>
     <mergeCell ref="C5:J5"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C8:J8"/>
